--- a/reports/load-test-report.xlsx
+++ b/reports/load-test-report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Load Performance 300" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Load Testing" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,7 +535,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 65ms, Avg: 250ms, Max: 1410ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 64ms, Avg: 226ms, Max: 1608ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 67ms, Avg: 241ms, Max: 1404ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 59ms, Avg: 259ms, Max: 1570ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 60ms, Avg: 255ms, Max: 1305ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 65ms, Avg: 261ms, Max: 1262ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 47ms, Avg: 277ms, Max: 1505ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 54ms, Avg: 242ms, Max: 1648ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 63ms, Avg: 254ms, Max: 1327ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 66ms, Avg: 259ms, Max: 1613ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 50ms, Avg: 287ms, Max: 1533ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 61ms, Avg: 247ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 48ms, Avg: 238ms, Max: 1574ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 53ms, Avg: 245ms, Max: 1403ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 48ms, Avg: 267ms, Max: 1572ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 73ms, Avg: 225ms, Max: 1460ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 66ms, Avg: 220ms, Max: 1591ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 60ms, Avg: 282ms, Max: 1547ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 46ms, Avg: 262ms, Max: 1263ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 70ms, Avg: 239ms, Max: 1274ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 63ms, Avg: 235ms, Max: 1580ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 68ms, Avg: 223ms, Max: 1454ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 57ms, Avg: 260ms, Max: 1525ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 47ms, Avg: 244ms, Max: 1577ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 63ms, Avg: 261ms, Max: 1642ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 67ms, Avg: 281ms, Max: 1346ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 49ms, Avg: 220ms, Max: 1621ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 54ms, Avg: 278ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 51ms, Avg: 224ms, Max: 1523ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 66ms, Avg: 269ms, Max: 1478ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 69ms, Avg: 286ms, Max: 1496ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 64ms, Avg: 286ms, Max: 1353ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 68ms, Avg: 277ms, Max: 1571ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 48ms, Avg: 242ms, Max: 1419ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 51ms, Avg: 274ms, Max: 1365ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 67ms, Avg: 242ms, Max: 1413ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 73ms, Avg: 254ms, Max: 1302ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 71ms, Avg: 236ms, Max: 1505ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 71ms, Avg: 286ms, Max: 1618ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 53ms, Avg: 256ms, Max: 1317ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 54ms, Avg: 288ms, Max: 1518ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 46ms, Avg: 249ms, Max: 1606ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 57ms, Avg: 287ms, Max: 1268ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 52ms, Avg: 281ms, Max: 1280ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 45ms, Avg: 285ms, Max: 1420ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 60ms, Avg: 231ms, Max: 1639ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 70ms, Avg: 268ms, Max: 1556ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 75ms, Avg: 241ms, Max: 1376ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 64ms, Avg: 276ms, Max: 1506ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 66ms, Avg: 290ms, Max: 1647ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 53ms, Avg: 241ms, Max: 1346ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 55ms, Avg: 263ms, Max: 1512ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 61ms, Avg: 273ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 71ms, Avg: 273ms, Max: 1401ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 69ms, Avg: 288ms, Max: 1416ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 67ms, Avg: 266ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 58ms, Avg: 259ms, Max: 1454ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 56ms, Avg: 274ms, Max: 1536ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 51ms, Avg: 245ms, Max: 1284ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 70ms, Avg: 281ms, Max: 1365ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 69ms, Avg: 263ms, Max: 1564ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 47ms, Avg: 266ms, Max: 1310ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 63ms, Avg: 244ms, Max: 1504ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 73ms, Avg: 242ms, Max: 1352ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 56ms, Avg: 229ms, Max: 1594ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 52ms, Avg: 254ms, Max: 1621ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 59ms, Avg: 224ms, Max: 1618ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 73ms, Avg: 251ms, Max: 1406ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 53ms, Avg: 270ms, Max: 1303ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 46ms, Avg: 231ms, Max: 1401ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 69ms, Avg: 236ms, Max: 1515ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 66ms, Avg: 252ms, Max: 1438ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 50ms, Avg: 258ms, Max: 1610ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 73ms, Avg: 267ms, Max: 1503ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 70ms, Avg: 242ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 54ms, Avg: 279ms, Max: 1447ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 48ms, Avg: 264ms, Max: 1295ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 56ms, Avg: 247ms, Max: 1250ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 68ms, Avg: 236ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 69ms, Avg: 224ms, Max: 1569ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 61ms, Avg: 234ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 73ms, Avg: 242ms, Max: 1353ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 50ms, Avg: 263ms, Max: 1495ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 65ms, Avg: 255ms, Max: 1550ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 56ms, Avg: 230ms, Max: 1374ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 56ms, Avg: 282ms, Max: 1417ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 58ms, Avg: 224ms, Max: 1333ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 56ms, Avg: 223ms, Max: 1444ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 56ms, Avg: 228ms, Max: 1644ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 49ms, Avg: 253ms, Max: 1343ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 64ms, Avg: 228ms, Max: 1314ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 50ms, Avg: 256ms, Max: 1345ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 66ms, Avg: 285ms, Max: 1602ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 64ms, Avg: 280ms, Max: 1309ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 49ms, Avg: 280ms, Max: 1420ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 53ms, Avg: 228ms, Max: 1626ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 63ms, Avg: 263ms, Max: 1275ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 56ms, Avg: 236ms, Max: 1482ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 55ms, Avg: 250ms, Max: 1334ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 58ms, Avg: 277ms, Max: 1329ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 45ms, Avg: 247ms, Max: 1419ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 71ms, Avg: 224ms, Max: 1562ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 45ms, Avg: 270ms, Max: 1306ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 62ms, Avg: 248ms, Max: 1307ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 51ms, Avg: 267ms, Max: 1556ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 66ms, Avg: 251ms, Max: 1579ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 59ms, Avg: 264ms, Max: 1515ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 60ms, Avg: 222ms, Max: 1553ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 55ms, Avg: 275ms, Max: 1538ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 69ms, Avg: 222ms, Max: 1592ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 63ms, Avg: 289ms, Max: 1619ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 46ms, Avg: 280ms, Max: 1358ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 55ms, Avg: 259ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 72ms, Avg: 256ms, Max: 1531ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 68ms, Avg: 280ms, Max: 1646ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 61ms, Avg: 285ms, Max: 1302ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 72ms, Avg: 289ms, Max: 1597ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 57ms, Avg: 280ms, Max: 1557ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 69ms, Avg: 255ms, Max: 1358ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 59ms, Avg: 242ms, Max: 1309ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 55ms, Avg: 287ms, Max: 1498ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 70ms, Avg: 231ms, Max: 1300ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 55ms, Avg: 254ms, Max: 1349ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 53ms, Avg: 290ms, Max: 1641ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 45ms, Avg: 221ms, Max: 1355ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 62ms, Avg: 221ms, Max: 1489ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 52ms, Avg: 270ms, Max: 1571ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 73ms, Avg: 249ms, Max: 1523ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 53ms, Avg: 281ms, Max: 1643ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 67ms, Avg: 221ms, Max: 1583ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 66ms, Avg: 277ms, Max: 1288ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 46ms, Avg: 253ms, Max: 1251ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 52ms, Avg: 233ms, Max: 1501ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 64ms, Avg: 230ms, Max: 1563ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 55ms, Avg: 237ms, Max: 1442ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 65ms, Avg: 255ms, Max: 1442ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 59ms, Avg: 288ms, Max: 1279ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 71ms, Avg: 229ms, Max: 1355ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 65ms, Avg: 258ms, Max: 1534ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 47ms, Avg: 222ms, Max: 1272ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 60ms, Avg: 238ms, Max: 1572ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 52ms, Avg: 224ms, Max: 1352ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 75ms, Avg: 278ms, Max: 1473ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 75ms, Avg: 255ms, Max: 1488ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 69ms, Avg: 269ms, Max: 1434ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 73ms, Avg: 226ms, Max: 1306ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 49ms, Avg: 275ms, Max: 1637ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 49ms, Avg: 246ms, Max: 1451ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 51ms, Avg: 232ms, Max: 1591ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 60ms, Avg: 279ms, Max: 1343ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 57ms, Avg: 281ms, Max: 1291ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 68ms, Avg: 243ms, Max: 1277ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 68ms, Avg: 250ms, Max: 1250ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 56ms, Avg: 258ms, Max: 1257ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 54ms, Avg: 273ms, Max: 1367ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 51ms, Avg: 284ms, Max: 1549ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 54ms, Avg: 224ms, Max: 1376ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 57ms, Avg: 235ms, Max: 1621ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 63ms, Avg: 248ms, Max: 1525ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 46ms, Avg: 278ms, Max: 1611ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 74ms, Avg: 234ms, Max: 1383ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 48ms, Avg: 225ms, Max: 1275ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 65ms, Avg: 277ms, Max: 1590ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 63ms, Avg: 247ms, Max: 1362ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 64ms, Avg: 285ms, Max: 1625ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 67ms, Avg: 237ms, Max: 1427ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 72ms, Avg: 266ms, Max: 1611ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 61ms, Avg: 287ms, Max: 1287ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 57ms, Avg: 251ms, Max: 1331ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 47ms, Avg: 275ms, Max: 1541ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 49ms, Avg: 239ms, Max: 1357ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 68ms, Avg: 286ms, Max: 1388ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 57ms, Avg: 284ms, Max: 1625ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 50ms, Avg: 241ms, Max: 1402ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 74ms, Avg: 234ms, Max: 1359ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 53ms, Avg: 249ms, Max: 1527ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 49ms, Avg: 269ms, Max: 1519ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 72ms, Avg: 255ms, Max: 1569ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 45ms, Avg: 268ms, Max: 1616ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 58ms, Avg: 241ms, Max: 1511ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 67ms, Avg: 247ms, Max: 1390ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 66ms, Avg: 241ms, Max: 1433ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 70ms, Avg: 227ms, Max: 1629ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 71ms, Avg: 251ms, Max: 1265ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 74ms, Avg: 267ms, Max: 1411ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 62ms, Avg: 273ms, Max: 1489ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 52ms, Avg: 239ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 75ms, Avg: 252ms, Max: 1274ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 72ms, Avg: 273ms, Max: 1287ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 49ms, Avg: 249ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 62ms, Avg: 272ms, Max: 1397ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 50ms, Avg: 279ms, Max: 1635ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 53ms, Avg: 234ms, Max: 1255ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 61ms, Avg: 248ms, Max: 1340ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 50ms, Avg: 276ms, Max: 1266ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 64ms, Avg: 274ms, Max: 1542ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 60ms, Avg: 285ms, Max: 1260ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 66ms, Avg: 246ms, Max: 1382ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 48ms, Avg: 254ms, Max: 1347ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 47ms, Avg: 263ms, Max: 1412ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 45ms, Avg: 268ms, Max: 1339ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 69ms, Avg: 230ms, Max: 1264ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 47ms, Avg: 266ms, Max: 1599ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 70ms, Avg: 261ms, Max: 1562ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 45ms, Avg: 229ms, Max: 1580ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 64ms, Avg: 255ms, Max: 1302ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 48ms, Avg: 259ms, Max: 1385ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 62ms, Avg: 280ms, Max: 1444ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 57ms, Avg: 264ms, Max: 1264ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 64ms, Avg: 277ms, Max: 1607ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 52ms, Avg: 227ms, Max: 1526ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 45ms, Avg: 257ms, Max: 1505ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 61ms, Avg: 281ms, Max: 1528ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 52ms, Avg: 230ms, Max: 1359ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 72ms, Avg: 228ms, Max: 1358ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 66ms, Avg: 285ms, Max: 1344ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 59ms, Avg: 242ms, Max: 1409ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 67ms, Avg: 230ms, Max: 1448ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 69ms, Avg: 263ms, Max: 1372ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 67ms, Avg: 271ms, Max: 1407ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 71ms, Avg: 237ms, Max: 1592ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 50ms, Avg: 270ms, Max: 1592ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 49ms, Avg: 230ms, Max: 1628ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 45ms, Avg: 224ms, Max: 1422ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 67ms, Avg: 280ms, Max: 1464ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 50ms, Avg: 230ms, Max: 1330ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 62ms, Avg: 273ms, Max: 1579ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 57ms, Avg: 231ms, Max: 1495ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 62ms, Avg: 261ms, Max: 1467ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 68ms, Avg: 269ms, Max: 1279ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 55ms, Avg: 248ms, Max: 1496ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 53ms, Avg: 250ms, Max: 1583ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 54ms, Avg: 254ms, Max: 1373ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 55ms, Avg: 233ms, Max: 1359ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 65ms, Avg: 256ms, Max: 1606ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 59ms, Avg: 270ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 49ms, Avg: 257ms, Max: 1511ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 50ms, Avg: 246ms, Max: 1395ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 54ms, Avg: 288ms, Max: 1321ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 69ms, Avg: 272ms, Max: 1619ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 61ms, Avg: 266ms, Max: 1586ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 66ms, Avg: 242ms, Max: 1462ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 58ms, Avg: 253ms, Max: 1361ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 57ms, Avg: 227ms, Max: 1476ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 66ms, Avg: 252ms, Max: 1419ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 70ms, Avg: 275ms, Max: 1335ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 50ms, Avg: 241ms, Max: 1445ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 53ms, Avg: 221ms, Max: 1519ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 54ms, Avg: 239ms, Max: 1491ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 60ms, Avg: 286ms, Max: 1315ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 71ms, Avg: 273ms, Max: 1534ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 67ms, Avg: 269ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 50ms, Avg: 228ms, Max: 1382ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 68ms, Avg: 228ms, Max: 1565ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 59ms, Avg: 243ms, Max: 1568ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 50ms, Avg: 282ms, Max: 1414ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 58ms, Avg: 246ms, Max: 1623ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 65ms, Avg: 257ms, Max: 1456ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 56ms, Avg: 238ms, Max: 1300ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 63ms, Avg: 251ms, Max: 1277ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 58ms, Avg: 221ms, Max: 1631ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 48ms, Avg: 251ms, Max: 1496ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 66ms, Avg: 278ms, Max: 1382ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 50ms, Avg: 227ms, Max: 1409ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 55ms, Avg: 271ms, Max: 1627ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 54ms, Avg: 288ms, Max: 1459ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 60ms, Avg: 272ms, Max: 1297ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 55ms, Avg: 235ms, Max: 1496ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 73ms, Avg: 275ms, Max: 1276ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 71ms, Avg: 229ms, Max: 1507ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 70ms, Avg: 228ms, Max: 1409ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 64ms, Avg: 266ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 71ms, Avg: 290ms, Max: 1434ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 48ms, Avg: 231ms, Max: 1386ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 60ms, Avg: 244ms, Max: 1349ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 59ms, Avg: 287ms, Max: 1280ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 59ms, Avg: 252ms, Max: 1383ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 47ms, Avg: 249ms, Max: 1554ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 66ms, Avg: 239ms, Max: 1547ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 73ms, Avg: 220ms, Max: 1511ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 50ms, Avg: 260ms, Max: 1467ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 58ms, Avg: 239ms, Max: 1493ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 49ms, Avg: 260ms, Max: 1623ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 62ms, Avg: 268ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 74ms, Avg: 237ms, Max: 1604ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 50ms, Avg: 226ms, Max: 1449ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 54ms, Avg: 236ms, Max: 1520ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 58ms, Avg: 257ms, Max: 1518ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 63ms, Avg: 228ms, Max: 1557ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 72ms, Avg: 281ms, Max: 1490ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 56ms, Avg: 256ms, Max: 1530ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 53ms, Avg: 230ms, Max: 1319ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 48ms, Avg: 269ms, Max: 1350ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 74ms, Avg: 253ms, Max: 1322ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 47ms, Avg: 242ms, Max: 1277ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 57ms, Avg: 235ms, Max: 1584ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 48ms, Avg: 260ms, Max: 1537ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 53ms, Avg: 247ms, Max: 1532ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 71ms, Avg: 236ms, Max: 1543ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 58ms, Avg: 221ms, Max: 1504ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 61ms, Avg: 250ms, Max: 1491ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 73ms, Avg: 234ms, Max: 1504ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 62ms, Avg: 253ms, Max: 1386ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 52ms, Avg: 225ms, Max: 1290ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 59ms, Avg: 237ms, Max: 1483ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 55ms, Avg: 280ms, Max: 1531ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 68ms, Avg: 243ms, Max: 1456ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 48ms, Avg: 263ms, Max: 1457ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 71ms, Avg: 283ms, Max: 1486ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 64ms, Avg: 253ms, Max: 1503ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 46ms, Avg: 267ms, Max: 1327ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 67ms, Avg: 272ms, Max: 1353ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 66ms, Avg: 237ms, Max: 1505ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 54ms, Avg: 227ms, Max: 1572ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 68ms, Avg: 220ms, Max: 1337ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 54ms, Avg: 273ms, Max: 1568ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 54ms, Avg: 257ms, Max: 1553ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 62ms, Avg: 258ms, Max: 1645ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 45ms, Avg: 231ms, Max: 1469ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 46ms, Avg: 244ms, Max: 1560ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 57ms, Avg: 222ms, Max: 1344ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 73ms, Avg: 244ms, Max: 1471ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 72ms, Avg: 227ms, Max: 1584ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 62ms, Avg: 271ms, Max: 1640ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 45ms, Avg: 222ms, Max: 1455ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 57ms, Avg: 278ms, Max: 1324ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 74ms, Avg: 221ms, Max: 1335ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 59ms, Avg: 233ms, Max: 1280ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 51ms, Avg: 272ms, Max: 1330ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 46ms, Avg: 239ms, Max: 1260ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 48ms, Avg: 280ms, Max: 1583ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 72ms, Avg: 267ms, Max: 1457ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 56ms, Avg: 251ms, Max: 1317ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 58ms, Avg: 273ms, Max: 1349ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 57ms, Avg: 286ms, Max: 1621ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 54ms, Avg: 278ms, Max: 1322ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 67ms, Avg: 241ms, Max: 1646ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 71ms, Avg: 264ms, Max: 1301ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 59ms, Avg: 270ms, Max: 1499ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 56ms, Avg: 264ms, Max: 1253ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 48ms, Avg: 249ms, Max: 1262ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 45ms, Avg: 281ms, Max: 1268ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 65ms, Avg: 255ms, Max: 1516ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 46ms, Avg: 253ms, Max: 1498ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 62ms, Avg: 274ms, Max: 1316ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 57ms, Avg: 226ms, Max: 1312ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 49ms, Avg: 226ms, Max: 1287ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 72ms, Avg: 288ms, Max: 1473ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 47ms, Avg: 254ms, Max: 1439ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 69ms, Avg: 260ms, Max: 1352ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 71ms, Avg: 254ms, Max: 1635ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 59ms, Avg: 229ms, Max: 1499ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 74ms, Avg: 264ms, Max: 1575ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 58ms, Avg: 277ms, Max: 1292ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 75ms, Avg: 267ms, Max: 1457ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 55ms, Avg: 253ms, Max: 1617ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 75ms, Avg: 263ms, Max: 1461ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 46ms, Avg: 227ms, Max: 1648ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 72ms, Avg: 264ms, Max: 1438ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 46ms, Avg: 255ms, Max: 1396ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 62ms, Avg: 281ms, Max: 1272ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 57ms, Avg: 243ms, Max: 1544ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 66ms, Avg: 238ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 47ms, Avg: 238ms, Max: 1315ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 73ms, Avg: 248ms, Max: 1569ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 66ms, Avg: 279ms, Max: 1441ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 74ms, Avg: 225ms, Max: 1355ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 56ms, Avg: 250ms, Max: 1450ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 62ms, Avg: 277ms, Max: 1529ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 55ms, Avg: 268ms, Max: 1536ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 57ms, Avg: 229ms, Max: 1447ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 49ms, Avg: 254ms, Max: 1436ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 61ms, Avg: 246ms, Max: 1577ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 68ms, Avg: 237ms, Max: 1308ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 57ms, Avg: 221ms, Max: 1641ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 66ms, Avg: 283ms, Max: 1336ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 58ms, Avg: 272ms, Max: 1331ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 68ms, Avg: 252ms, Max: 1317ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 58ms, Avg: 286ms, Max: 1482ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 47ms, Avg: 246ms, Max: 1313ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 48ms, Avg: 262ms, Max: 1408ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 63ms, Avg: 250ms, Max: 1636ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 75ms, Avg: 239ms, Max: 1633ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 55ms, Avg: 222ms, Max: 1519ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 55ms, Avg: 228ms, Max: 1476ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 54ms, Avg: 269ms, Max: 1252ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 59ms, Avg: 227ms, Max: 1359ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 68ms, Avg: 226ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 48ms, Avg: 284ms, Max: 1261ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 72ms, Avg: 261ms, Max: 1554ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 65ms, Avg: 278ms, Max: 1326ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 46ms, Avg: 246ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 56ms, Avg: 288ms, Max: 1327ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 70ms, Avg: 288ms, Max: 1508ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 56ms, Avg: 274ms, Max: 1622ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 70ms, Avg: 261ms, Max: 1281ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 45ms, Avg: 267ms, Max: 1422ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 46ms, Avg: 236ms, Max: 1389ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 51ms, Avg: 286ms, Max: 1270ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 59ms, Avg: 269ms, Max: 1400ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 65ms, Avg: 280ms, Max: 1636ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 58ms, Avg: 226ms, Max: 1390ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 61ms, Avg: 228ms, Max: 1584ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 71ms, Avg: 226ms, Max: 1586ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 63ms, Avg: 262ms, Max: 1287ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 47ms, Avg: 241ms, Max: 1265ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 47ms, Avg: 284ms, Max: 1272ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 55ms, Avg: 267ms, Max: 1632ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 71ms, Avg: 278ms, Max: 1300ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 47ms, Avg: 231ms, Max: 1314ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 60ms, Avg: 262ms, Max: 1637ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 68ms, Avg: 252ms, Max: 1492ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 63ms, Avg: 283ms, Max: 1306ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 73ms, Avg: 255ms, Max: 1368ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 46ms, Avg: 289ms, Max: 1504ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 67ms, Avg: 263ms, Max: 1319ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 63ms, Avg: 231ms, Max: 1599ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 56ms, Avg: 288ms, Max: 1649ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 50ms, Avg: 256ms, Max: 1347ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 48ms, Avg: 287ms, Max: 1589ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 57ms, Avg: 238ms, Max: 1530ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 59ms, Avg: 240ms, Max: 1455ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 57ms, Avg: 246ms, Max: 1264ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 70ms, Avg: 249ms, Max: 1341ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 73ms, Avg: 262ms, Max: 1611ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 45ms, Avg: 241ms, Max: 1270ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 62ms, Avg: 283ms, Max: 1417ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 46ms, Avg: 258ms, Max: 1507ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 71ms, Avg: 272ms, Max: 1464ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 50ms, Avg: 235ms, Max: 1297ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 62ms, Avg: 236ms, Max: 1523ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 64ms, Avg: 241ms, Max: 1475ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 66ms, Avg: 262ms, Max: 1428ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 62ms, Avg: 240ms, Max: 1525ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 59ms, Avg: 222ms, Max: 1576ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 59ms, Avg: 257ms, Max: 1500ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 46ms, Avg: 264ms, Max: 1592ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 52ms, Avg: 284ms, Max: 1251ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 73ms, Avg: 234ms, Max: 1649ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 64ms, Avg: 225ms, Max: 1573ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 71ms, Avg: 245ms, Max: 1382ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 73ms, Avg: 284ms, Max: 1393ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 73ms, Avg: 270ms, Max: 1550ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 68ms, Avg: 229ms, Max: 1540ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 74ms, Avg: 256ms, Max: 1641ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 52ms, Avg: 262ms, Max: 1635ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 52ms, Avg: 257ms, Max: 1297ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 48ms, Avg: 237ms, Max: 1546ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 54ms, Avg: 273ms, Max: 1602ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 72ms, Avg: 252ms, Max: 1420ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 58ms, Avg: 274ms, Max: 1623ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 60ms, Avg: 255ms, Max: 1445ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 45ms, Avg: 249ms, Max: 1577ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 48ms, Avg: 233ms, Max: 1581ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 46ms, Avg: 238ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 61ms, Avg: 237ms, Max: 1318ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 72ms, Avg: 257ms, Max: 1432ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 63ms, Avg: 265ms, Max: 1534ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 65ms, Avg: 247ms, Max: 1286ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 73ms, Avg: 258ms, Max: 1599ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 72ms, Avg: 276ms, Max: 1320ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 65ms, Avg: 274ms, Max: 1268ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 48ms, Avg: 248ms, Max: 1422ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 70ms, Avg: 265ms, Max: 1428ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 48ms, Avg: 222ms, Max: 1292ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 65ms, Avg: 283ms, Max: 1512ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 69ms, Avg: 271ms, Max: 1451ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 58ms, Avg: 267ms, Max: 1501ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 59ms, Avg: 264ms, Max: 1594ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 60ms, Avg: 232ms, Max: 1390ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 56ms, Avg: 235ms, Max: 1495ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 72ms, Avg: 229ms, Max: 1529ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 59ms, Avg: 247ms, Max: 1493ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 68ms, Avg: 269ms, Max: 1414ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 67ms, Avg: 286ms, Max: 1441ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 52ms, Avg: 243ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 69ms, Avg: 265ms, Max: 1517ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 66ms, Avg: 266ms, Max: 1280ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 64ms, Avg: 226ms, Max: 1556ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 60ms, Avg: 250ms, Max: 1649ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 51ms, Avg: 290ms, Max: 1508ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 72ms, Avg: 233ms, Max: 1324ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 55ms, Avg: 285ms, Max: 1615ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 54ms, Avg: 285ms, Max: 1467ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 65ms, Avg: 251ms, Max: 1513ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 64ms, Avg: 234ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 58ms, Avg: 279ms, Max: 1320ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 58ms, Avg: 277ms, Max: 1603ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 61ms, Avg: 230ms, Max: 1640ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 60ms, Avg: 222ms, Max: 1340ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 47ms, Avg: 267ms, Max: 1405ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 50ms, Avg: 261ms, Max: 1278ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 66ms, Avg: 283ms, Max: 1619ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 52ms, Avg: 266ms, Max: 1303ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 75ms, Avg: 285ms, Max: 1593ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 47ms, Avg: 290ms, Max: 1515ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 67ms, Avg: 227ms, Max: 1282ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 74ms, Avg: 249ms, Max: 1421ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 59ms, Avg: 223ms, Max: 1351ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 68ms, Avg: 286ms, Max: 1428ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 61ms, Avg: 239ms, Max: 1635ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 70ms, Avg: 251ms, Max: 1305ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 51ms, Avg: 222ms, Max: 1617ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 47ms, Avg: 266ms, Max: 1368ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 45ms, Avg: 262ms, Max: 1534ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 47ms, Avg: 240ms, Max: 1636ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 65ms, Avg: 270ms, Max: 1308ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 54ms, Avg: 228ms, Max: 1320ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 68ms, Avg: 233ms, Max: 1647ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 66ms, Avg: 261ms, Max: 1545ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 50ms, Avg: 252ms, Max: 1449ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 71ms, Avg: 252ms, Max: 1349ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 54ms, Avg: 241ms, Max: 1436ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 73ms, Avg: 267ms, Max: 1491ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 47ms, Avg: 279ms, Max: 1515ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 46ms, Avg: 228ms, Max: 1647ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 53ms, Avg: 240ms, Max: 1306ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 72ms, Avg: 267ms, Max: 1273ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 69ms, Avg: 279ms, Max: 1564ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 45ms, Avg: 254ms, Max: 1356ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 66ms, Avg: 249ms, Max: 1593ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 73ms, Avg: 251ms, Max: 1274ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 68ms, Avg: 244ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 56ms, Avg: 281ms, Max: 1481ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 74ms, Avg: 254ms, Max: 1283ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 73ms, Avg: 256ms, Max: 1364ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 48ms, Avg: 269ms, Max: 1617ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 54ms, Avg: 277ms, Max: 1506ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 74ms, Avg: 276ms, Max: 1445ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 59ms, Avg: 238ms, Max: 1342ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 56ms, Avg: 241ms, Max: 1637ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 72ms, Avg: 222ms, Max: 1610ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 73ms, Avg: 237ms, Max: 1573ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 47ms, Avg: 270ms, Max: 1453ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 52ms, Avg: 268ms, Max: 1624ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 67ms, Avg: 273ms, Max: 1581ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 45ms, Avg: 246ms, Max: 1529ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 71ms, Avg: 220ms, Max: 1645ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 51ms, Avg: 265ms, Max: 1614ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 58ms, Avg: 238ms, Max: 1399ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 46ms, Avg: 262ms, Max: 1342ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 72ms, Avg: 221ms, Max: 1450ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 63ms, Avg: 254ms, Max: 1352ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 66ms, Avg: 248ms, Max: 1337ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -15179,7 +15179,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 46ms, Avg: 260ms, Max: 1596ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 56ms, Avg: 266ms, Max: 1351ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 59ms, Avg: 243ms, Max: 1476ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 54ms, Avg: 244ms, Max: 1521ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 56ms, Avg: 231ms, Max: 1452ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 53ms, Avg: 241ms, Max: 1562ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 61ms, Avg: 271ms, Max: 1506ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 71ms, Avg: 260ms, Max: 1420ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 54ms, Avg: 286ms, Max: 1641ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 68ms, Avg: 229ms, Max: 1258ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 59ms, Avg: 248ms, Max: 1518ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 75ms, Avg: 240ms, Max: 1295ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 62ms, Avg: 286ms, Max: 1269ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 71ms, Avg: 256ms, Max: 1585ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 64ms, Avg: 278ms, Max: 1450ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 58ms, Avg: 269ms, Max: 1503ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 45ms, Avg: 257ms, Max: 1598ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 64ms, Avg: 248ms, Max: 1312ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 59ms, Avg: 228ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 68ms, Avg: 254ms, Max: 1554ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -15719,7 +15719,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 62ms, Avg: 223ms, Max: 1289ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 57ms, Avg: 287ms, Max: 1633ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 54ms, Avg: 275ms, Max: 1586ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 68ms, Avg: 229ms, Max: 1290ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 57ms, Avg: 258ms, Max: 1430ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 70ms, Avg: 227ms, Max: 1490ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 68ms, Avg: 242ms, Max: 1328ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 59ms, Avg: 262ms, Max: 1430ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 66ms, Avg: 237ms, Max: 1541ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 63ms, Avg: 245ms, Max: 1284ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 56ms, Avg: 276ms, Max: 1602ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 69ms, Avg: 231ms, Max: 1613ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 49ms, Avg: 281ms, Max: 1608ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 55ms, Avg: 258ms, Max: 1616ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 61ms, Avg: 256ms, Max: 1305ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 64ms, Avg: 235ms, Max: 1626ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 53ms, Avg: 266ms, Max: 1577ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 65ms, Avg: 286ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 74ms, Avg: 241ms, Max: 1418ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 52ms, Avg: 290ms, Max: 1288ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 57ms, Avg: 267ms, Max: 1338ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 64ms, Avg: 257ms, Max: 1419ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 59ms, Avg: 223ms, Max: 1443ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 70ms, Avg: 252ms, Max: 1504ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 45ms, Avg: 221ms, Max: 1628ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 64ms, Avg: 273ms, Max: 1412ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 53ms, Avg: 254ms, Max: 1540ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 65ms, Avg: 279ms, Max: 1631ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 56ms, Avg: 267ms, Max: 1598ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 61ms, Avg: 276ms, Max: 1614ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 64ms, Avg: 226ms, Max: 1459ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 71ms, Avg: 275ms, Max: 1624ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 65ms, Avg: 228ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 72ms, Avg: 263ms, Max: 1526ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 68ms, Avg: 242ms, Max: 1390ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 46ms, Avg: 228ms, Max: 1395ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">

--- a/reports/load-test-report.xlsx
+++ b/reports/load-test-report.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 64ms, Avg: 226ms, Max: 1608ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 46ms, Avg: 232ms, Max: 1277ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -545,12 +545,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 59ms, Avg: 259ms, Max: 1570ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 46ms, Avg: 282ms, Max: 1546ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 65ms, Avg: 261ms, Max: 1262ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 75ms, Avg: 230ms, Max: 1380ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 54ms, Avg: 242ms, Max: 1648ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 46ms, Avg: 260ms, Max: 1528ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 66ms, Avg: 259ms, Max: 1613ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 75ms, Avg: 246ms, Max: 1314ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 61ms, Avg: 247ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 46ms, Avg: 245ms, Max: 1619ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 53ms, Avg: 245ms, Max: 1403ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 73ms, Avg: 259ms, Max: 1582ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 73ms, Avg: 225ms, Max: 1460ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 47ms, Avg: 275ms, Max: 1552ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 60ms, Avg: 282ms, Max: 1547ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 52ms, Avg: 277ms, Max: 1493ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 70ms, Avg: 239ms, Max: 1274ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 73ms, Avg: 245ms, Max: 1407ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 68ms, Avg: 223ms, Max: 1454ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 53ms, Avg: 231ms, Max: 1326ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 47ms, Avg: 244ms, Max: 1577ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 73ms, Avg: 223ms, Max: 1326ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 67ms, Avg: 281ms, Max: 1346ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 49ms, Avg: 222ms, Max: 1252ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 54ms, Avg: 278ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 71ms, Avg: 233ms, Max: 1543ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:45</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 66ms, Avg: 269ms, Max: 1478ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 71ms, Avg: 220ms, Max: 1575ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 64ms, Avg: 286ms, Max: 1353ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 60ms, Avg: 267ms, Max: 1624ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 48ms, Avg: 242ms, Max: 1419ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 65ms, Avg: 289ms, Max: 1296ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 67ms, Avg: 242ms, Max: 1413ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 73ms, Avg: 237ms, Max: 1318ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 71ms, Avg: 236ms, Max: 1505ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 70ms, Avg: 247ms, Max: 1428ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:36</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 53ms, Avg: 256ms, Max: 1317ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 52ms, Avg: 251ms, Max: 1519ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:29</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 46ms, Avg: 249ms, Max: 1606ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 70ms, Avg: 238ms, Max: 1394ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:43</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 52ms, Avg: 281ms, Max: 1280ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 73ms, Avg: 252ms, Max: 1422ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 60ms, Avg: 231ms, Max: 1639ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 57ms, Avg: 231ms, Max: 1587ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:35</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 75ms, Avg: 241ms, Max: 1376ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 61ms, Avg: 267ms, Max: 1319ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 66ms, Avg: 290ms, Max: 1647ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 61ms, Avg: 235ms, Max: 1454ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:36</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 55ms, Avg: 263ms, Max: 1512ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 70ms, Avg: 246ms, Max: 1339ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:38</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 71ms, Avg: 273ms, Max: 1401ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 73ms, Avg: 273ms, Max: 1577ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:22</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 67ms, Avg: 266ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 54ms, Avg: 282ms, Max: 1288ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:42</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 56ms, Avg: 274ms, Max: 1536ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 75ms, Avg: 255ms, Max: 1398ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:46</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 70ms, Avg: 281ms, Max: 1365ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 50ms, Avg: 276ms, Max: 1548ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 47ms, Avg: 266ms, Max: 1310ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 75ms, Avg: 229ms, Max: 1327ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:48</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 73ms, Avg: 242ms, Max: 1352ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 72ms, Avg: 251ms, Max: 1567ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:03</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 52ms, Avg: 254ms, Max: 1621ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 69ms, Avg: 262ms, Max: 1458ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:52</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 73ms, Avg: 251ms, Max: 1406ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 54ms, Avg: 283ms, Max: 1308ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 46ms, Avg: 231ms, Max: 1401ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 49ms, Avg: 266ms, Max: 1333ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:41</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 66ms, Avg: 252ms, Max: 1438ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 51ms, Avg: 261ms, Max: 1308ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:21</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 73ms, Avg: 267ms, Max: 1503ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 54ms, Avg: 276ms, Max: 1261ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:19</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 54ms, Avg: 279ms, Max: 1447ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 59ms, Avg: 233ms, Max: 1474ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:16</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 56ms, Avg: 247ms, Max: 1250ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 52ms, Avg: 283ms, Max: 1493ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:37</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 69ms, Avg: 224ms, Max: 1569ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 70ms, Avg: 225ms, Max: 1606ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 73ms, Avg: 242ms, Max: 1353ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 58ms, Avg: 265ms, Max: 1475ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:17</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 65ms, Avg: 255ms, Max: 1550ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 72ms, Avg: 229ms, Max: 1579ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:43</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 56ms, Avg: 282ms, Max: 1417ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 70ms, Avg: 258ms, Max: 1315ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:45</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 56ms, Avg: 223ms, Max: 1444ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 59ms, Avg: 236ms, Max: 1309ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:02</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 49ms, Avg: 253ms, Max: 1343ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 63ms, Avg: 258ms, Max: 1505ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:57</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 50ms, Avg: 256ms, Max: 1345ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 50ms, Avg: 230ms, Max: 1356ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:18</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 64ms, Avg: 280ms, Max: 1309ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 73ms, Avg: 268ms, Max: 1639ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:21</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 53ms, Avg: 228ms, Max: 1626ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 50ms, Avg: 241ms, Max: 1569ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:35</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 56ms, Avg: 236ms, Max: 1482ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 66ms, Avg: 267ms, Max: 1597ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:27</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 58ms, Avg: 277ms, Max: 1329ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 59ms, Avg: 279ms, Max: 1582ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:18</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 71ms, Avg: 224ms, Max: 1562ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 48ms, Avg: 283ms, Max: 1291ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:04</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 62ms, Avg: 248ms, Max: 1307ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 71ms, Avg: 248ms, Max: 1502ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:56</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 66ms, Avg: 251ms, Max: 1579ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 58ms, Avg: 233ms, Max: 1442ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:41</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 60ms, Avg: 222ms, Max: 1553ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 60ms, Avg: 259ms, Max: 1450ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:37</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 69ms, Avg: 222ms, Max: 1592ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 64ms, Avg: 288ms, Max: 1544ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:34</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 46ms, Avg: 280ms, Max: 1358ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 70ms, Avg: 253ms, Max: 1639ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:51</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 72ms, Avg: 256ms, Max: 1531ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 65ms, Avg: 285ms, Max: 1415ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:32</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 61ms, Avg: 285ms, Max: 1302ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 71ms, Avg: 288ms, Max: 1321ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:05</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 57ms, Avg: 280ms, Max: 1557ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 51ms, Avg: 273ms, Max: 1548ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:38</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 59ms, Avg: 242ms, Max: 1309ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 55ms, Avg: 265ms, Max: 1325ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3731,12 +3731,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:51</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 70ms, Avg: 231ms, Max: 1300ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 71ms, Avg: 244ms, Max: 1362ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:01</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 53ms, Avg: 290ms, Max: 1641ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 74ms, Avg: 232ms, Max: 1382ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:57</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 62ms, Avg: 221ms, Max: 1489ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 67ms, Avg: 227ms, Max: 1589ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 73ms, Avg: 249ms, Max: 1523ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 53ms, Avg: 267ms, Max: 1282ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:04</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 67ms, Avg: 221ms, Max: 1583ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 58ms, Avg: 289ms, Max: 1412ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:46</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 46ms, Avg: 253ms, Max: 1251ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 67ms, Avg: 268ms, Max: 1546ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:35</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 64ms, Avg: 230ms, Max: 1563ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 50ms, Avg: 244ms, Max: 1262ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:11</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 65ms, Avg: 255ms, Max: 1442ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 58ms, Avg: 271ms, Max: 1618ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:29</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 71ms, Avg: 229ms, Max: 1355ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 66ms, Avg: 289ms, Max: 1313ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:29</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 47ms, Avg: 222ms, Max: 1272ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 46ms, Avg: 229ms, Max: 1599ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:04</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 52ms, Avg: 224ms, Max: 1352ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 75ms, Avg: 222ms, Max: 1429ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:59</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 75ms, Avg: 255ms, Max: 1488ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 61ms, Avg: 286ms, Max: 1259ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:28</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 73ms, Avg: 226ms, Max: 1306ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 59ms, Avg: 260ms, Max: 1365ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:35</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 49ms, Avg: 246ms, Max: 1451ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 73ms, Avg: 246ms, Max: 1362ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:16</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 60ms, Avg: 279ms, Max: 1343ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 64ms, Avg: 263ms, Max: 1406ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:55</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 68ms, Avg: 243ms, Max: 1277ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 55ms, Avg: 247ms, Max: 1541ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:17</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 56ms, Avg: 258ms, Max: 1257ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 62ms, Avg: 288ms, Max: 1294ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:04</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 51ms, Avg: 284ms, Max: 1549ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 45ms, Avg: 240ms, Max: 1538ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:58</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 57ms, Avg: 235ms, Max: 1621ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 49ms, Avg: 244ms, Max: 1467ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:11</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 46ms, Avg: 278ms, Max: 1611ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 52ms, Avg: 242ms, Max: 1340ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:49</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 48ms, Avg: 225ms, Max: 1275ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 52ms, Avg: 247ms, Max: 1444ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4865,12 +4865,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:39</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 63ms, Avg: 247ms, Max: 1362ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 61ms, Avg: 259ms, Max: 1618ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:29</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 67ms, Avg: 237ms, Max: 1427ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 57ms, Avg: 227ms, Max: 1347ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:55</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 61ms, Avg: 287ms, Max: 1287ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 53ms, Avg: 274ms, Max: 1463ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:53</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 47ms, Avg: 275ms, Max: 1541ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 58ms, Avg: 276ms, Max: 1318ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 68ms, Avg: 286ms, Max: 1388ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 66ms, Avg: 241ms, Max: 1429ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:48</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 50ms, Avg: 241ms, Max: 1402ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 45ms, Avg: 272ms, Max: 1345ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:20</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 53ms, Avg: 249ms, Max: 1527ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 65ms, Avg: 248ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:35</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 72ms, Avg: 255ms, Max: 1569ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 68ms, Avg: 270ms, Max: 1597ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:50</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 58ms, Avg: 241ms, Max: 1511ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 68ms, Avg: 285ms, Max: 1314ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:04</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 66ms, Avg: 241ms, Max: 1433ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 45ms, Avg: 276ms, Max: 1344ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:35</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 71ms, Avg: 251ms, Max: 1265ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 71ms, Avg: 245ms, Max: 1448ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:02</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 62ms, Avg: 273ms, Max: 1489ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 55ms, Avg: 227ms, Max: 1459ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:34</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 75ms, Avg: 252ms, Max: 1274ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 52ms, Avg: 252ms, Max: 1595ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:04</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 49ms, Avg: 249ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 67ms, Avg: 290ms, Max: 1267ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:36</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 50ms, Avg: 279ms, Max: 1635ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 48ms, Avg: 223ms, Max: 1328ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:14</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 61ms, Avg: 248ms, Max: 1340ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 50ms, Avg: 270ms, Max: 1455ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:31</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 64ms, Avg: 274ms, Max: 1542ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 68ms, Avg: 285ms, Max: 1626ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:31</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 66ms, Avg: 246ms, Max: 1382ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 66ms, Avg: 280ms, Max: 1421ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:24</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 47ms, Avg: 263ms, Max: 1412ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 57ms, Avg: 268ms, Max: 1428ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:12</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 69ms, Avg: 230ms, Max: 1264ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 49ms, Avg: 233ms, Max: 1568ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:41</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 70ms, Avg: 261ms, Max: 1562ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 50ms, Avg: 230ms, Max: 1543ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:57</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 64ms, Avg: 255ms, Max: 1302ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 65ms, Avg: 283ms, Max: 1344ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:50</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 62ms, Avg: 280ms, Max: 1444ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 64ms, Avg: 232ms, Max: 1564ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:37</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 64ms, Avg: 277ms, Max: 1607ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 54ms, Avg: 235ms, Max: 1462ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:04</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 45ms, Avg: 257ms, Max: 1505ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 47ms, Avg: 276ms, Max: 1565ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:32</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 52ms, Avg: 230ms, Max: 1359ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 48ms, Avg: 271ms, Max: 1355ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:26</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 66ms, Avg: 285ms, Max: 1344ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 60ms, Avg: 278ms, Max: 1434ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:01</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 67ms, Avg: 230ms, Max: 1448ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 54ms, Avg: 286ms, Max: 1487ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:36</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 67ms, Avg: 271ms, Max: 1407ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 75ms, Avg: 255ms, Max: 1633ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:53</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 50ms, Avg: 270ms, Max: 1592ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 63ms, Avg: 260ms, Max: 1353ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:07</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 45ms, Avg: 224ms, Max: 1422ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 66ms, Avg: 260ms, Max: 1475ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -6539,12 +6539,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:19</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 50ms, Avg: 230ms, Max: 1330ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 56ms, Avg: 272ms, Max: 1432ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:45</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 57ms, Avg: 231ms, Max: 1495ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 75ms, Avg: 246ms, Max: 1444ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:33</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 68ms, Avg: 269ms, Max: 1279ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 64ms, Avg: 267ms, Max: 1463ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:33</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 53ms, Avg: 250ms, Max: 1583ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 66ms, Avg: 225ms, Max: 1374ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 55ms, Avg: 233ms, Max: 1359ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 46ms, Avg: 223ms, Max: 1374ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:38</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 59ms, Avg: 270ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 60ms, Avg: 289ms, Max: 1535ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:52</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 50ms, Avg: 246ms, Max: 1395ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 69ms, Avg: 266ms, Max: 1261ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:31</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 69ms, Avg: 272ms, Max: 1619ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 54ms, Avg: 269ms, Max: 1338ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:30</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 66ms, Avg: 242ms, Max: 1462ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 67ms, Avg: 270ms, Max: 1353ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:47</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 57ms, Avg: 227ms, Max: 1476ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 55ms, Avg: 234ms, Max: 1507ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:49</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 70ms, Avg: 275ms, Max: 1335ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 75ms, Avg: 233ms, Max: 1640ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:08</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 53ms, Avg: 221ms, Max: 1519ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 50ms, Avg: 275ms, Max: 1267ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:03</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 60ms, Avg: 286ms, Max: 1315ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 58ms, Avg: 283ms, Max: 1376ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:13</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 67ms, Avg: 269ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 68ms, Avg: 265ms, Max: 1625ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:40</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 68ms, Avg: 228ms, Max: 1565ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 62ms, Avg: 264ms, Max: 1379ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:07</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 50ms, Avg: 282ms, Max: 1414ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 65ms, Avg: 239ms, Max: 1507ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:29</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 65ms, Avg: 257ms, Max: 1456ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 46ms, Avg: 276ms, Max: 1529ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:08</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 63ms, Avg: 251ms, Max: 1277ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 63ms, Avg: 234ms, Max: 1536ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:46</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 48ms, Avg: 251ms, Max: 1496ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 68ms, Avg: 243ms, Max: 1303ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:39</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 50ms, Avg: 227ms, Max: 1409ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 57ms, Avg: 277ms, Max: 1303ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:03</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 54ms, Avg: 288ms, Max: 1459ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 61ms, Avg: 280ms, Max: 1624ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:11</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 55ms, Avg: 235ms, Max: 1496ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 74ms, Avg: 245ms, Max: 1301ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:26</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 71ms, Avg: 229ms, Max: 1507ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 75ms, Avg: 226ms, Max: 1572ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -7781,12 +7781,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:56</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 64ms, Avg: 266ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 71ms, Avg: 279ms, Max: 1496ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:32</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 48ms, Avg: 231ms, Max: 1386ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 54ms, Avg: 262ms, Max: 1399ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -7889,12 +7889,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:06</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 59ms, Avg: 287ms, Max: 1280ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 45ms, Avg: 283ms, Max: 1430ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:13</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 47ms, Avg: 249ms, Max: 1554ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 72ms, Avg: 283ms, Max: 1631ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:08</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 73ms, Avg: 220ms, Max: 1511ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 52ms, Avg: 250ms, Max: 1643ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:20</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 58ms, Avg: 239ms, Max: 1493ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 70ms, Avg: 281ms, Max: 1643ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:03</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 62ms, Avg: 268ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 54ms, Avg: 259ms, Max: 1442ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:03</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 50ms, Avg: 226ms, Max: 1449ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 67ms, Avg: 231ms, Max: 1429ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:43</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 58ms, Avg: 257ms, Max: 1518ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 53ms, Avg: 224ms, Max: 1390ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:04</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 72ms, Avg: 281ms, Max: 1490ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 53ms, Avg: 253ms, Max: 1444ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:04</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 53ms, Avg: 230ms, Max: 1319ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 52ms, Avg: 235ms, Max: 1490ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:20</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 74ms, Avg: 253ms, Max: 1322ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 61ms, Avg: 285ms, Max: 1551ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:50</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 57ms, Avg: 235ms, Max: 1584ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 59ms, Avg: 221ms, Max: 1510ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:55</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 53ms, Avg: 247ms, Max: 1532ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 74ms, Avg: 251ms, Max: 1454ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:14</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 58ms, Avg: 221ms, Max: 1504ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 51ms, Avg: 263ms, Max: 1629ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:32</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 73ms, Avg: 234ms, Max: 1504ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 70ms, Avg: 239ms, Max: 1620ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:40</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 52ms, Avg: 225ms, Max: 1290ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 45ms, Avg: 255ms, Max: 1380ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:46</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 55ms, Avg: 280ms, Max: 1531ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 60ms, Avg: 269ms, Max: 1281ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:15</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 48ms, Avg: 263ms, Max: 1457ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 53ms, Avg: 246ms, Max: 1571ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:47</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 64ms, Avg: 253ms, Max: 1503ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 51ms, Avg: 271ms, Max: 1287ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:34</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 67ms, Avg: 272ms, Max: 1353ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 55ms, Avg: 240ms, Max: 1519ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:18</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 54ms, Avg: 227ms, Max: 1572ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 66ms, Avg: 229ms, Max: 1612ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:33</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 54ms, Avg: 273ms, Max: 1568ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 52ms, Avg: 220ms, Max: 1329ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:01</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 62ms, Avg: 258ms, Max: 1645ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 57ms, Avg: 276ms, Max: 1372ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:55</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 46ms, Avg: 244ms, Max: 1560ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 68ms, Avg: 230ms, Max: 1500ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:23</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 73ms, Avg: 244ms, Max: 1471ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 63ms, Avg: 264ms, Max: 1571ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:08</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 62ms, Avg: 271ms, Max: 1640ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 73ms, Avg: 226ms, Max: 1368ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:08</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 57ms, Avg: 278ms, Max: 1324ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 53ms, Avg: 227ms, Max: 1278ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:39</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 59ms, Avg: 233ms, Max: 1280ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 69ms, Avg: 246ms, Max: 1377ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:11</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 46ms, Avg: 239ms, Max: 1260ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 75ms, Avg: 280ms, Max: 1647ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:15</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 72ms, Avg: 267ms, Max: 1457ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 71ms, Avg: 228ms, Max: 1631ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -9455,12 +9455,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:19</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 58ms, Avg: 273ms, Max: 1349ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 46ms, Avg: 235ms, Max: 1617ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:11</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 54ms, Avg: 278ms, Max: 1322ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 66ms, Avg: 249ms, Max: 1346ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:29</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 71ms, Avg: 264ms, Max: 1301ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 51ms, Avg: 230ms, Max: 1528ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:23</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 56ms, Avg: 264ms, Max: 1253ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 66ms, Avg: 246ms, Max: 1272ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:04</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 45ms, Avg: 281ms, Max: 1268ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 74ms, Avg: 236ms, Max: 1541ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:11</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 46ms, Avg: 253ms, Max: 1498ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 60ms, Avg: 251ms, Max: 1575ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:55</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 57ms, Avg: 226ms, Max: 1312ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 67ms, Avg: 255ms, Max: 1516ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:58</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 72ms, Avg: 288ms, Max: 1473ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 51ms, Avg: 229ms, Max: 1284ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:32</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 69ms, Avg: 260ms, Max: 1352ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 63ms, Avg: 264ms, Max: 1371ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -9941,12 +9941,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:04</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 59ms, Avg: 229ms, Max: 1499ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 65ms, Avg: 281ms, Max: 1312ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:14</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 58ms, Avg: 277ms, Max: 1292ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 72ms, Avg: 250ms, Max: 1383ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:40</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 55ms, Avg: 253ms, Max: 1617ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 72ms, Avg: 221ms, Max: 1631ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:50</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 46ms, Avg: 227ms, Max: 1648ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 68ms, Avg: 243ms, Max: 1374ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:47</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 46ms, Avg: 255ms, Max: 1396ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 51ms, Avg: 265ms, Max: 1372ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:01</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 57ms, Avg: 243ms, Max: 1544ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 51ms, Avg: 227ms, Max: 1645ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 47ms, Avg: 238ms, Max: 1315ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 58ms, Avg: 271ms, Max: 1292ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:36</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 66ms, Avg: 279ms, Max: 1441ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 64ms, Avg: 246ms, Max: 1414ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:41</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 56ms, Avg: 250ms, Max: 1450ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 72ms, Avg: 256ms, Max: 1336ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:31</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 55ms, Avg: 268ms, Max: 1536ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 75ms, Avg: 241ms, Max: 1397ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:42</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 49ms, Avg: 254ms, Max: 1436ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 71ms, Avg: 254ms, Max: 1394ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -10535,12 +10535,12 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:27</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 68ms, Avg: 237ms, Max: 1308ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 58ms, Avg: 289ms, Max: 1521ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:45</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 66ms, Avg: 283ms, Max: 1336ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 46ms, Avg: 256ms, Max: 1603ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:05</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 68ms, Avg: 252ms, Max: 1317ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 52ms, Avg: 279ms, Max: 1329ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:47</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 47ms, Avg: 246ms, Max: 1313ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 63ms, Avg: 289ms, Max: 1270ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:27</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 63ms, Avg: 250ms, Max: 1636ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 68ms, Avg: 262ms, Max: 1463ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:26</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 55ms, Avg: 222ms, Max: 1519ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 69ms, Avg: 278ms, Max: 1387ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:04</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 54ms, Avg: 269ms, Max: 1252ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 53ms, Avg: 290ms, Max: 1542ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:26</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 68ms, Avg: 226ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 50ms, Avg: 259ms, Max: 1390ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -10967,12 +10967,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:41</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 72ms, Avg: 261ms, Max: 1554ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 50ms, Avg: 268ms, Max: 1566ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:36</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 46ms, Avg: 246ms, Max: 1484ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 51ms, Avg: 227ms, Max: 1594ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:06</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 70ms, Avg: 288ms, Max: 1508ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 67ms, Avg: 281ms, Max: 1633ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:53</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 70ms, Avg: 261ms, Max: 1281ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 56ms, Avg: 222ms, Max: 1303ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:14</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 46ms, Avg: 236ms, Max: 1389ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 53ms, Avg: 223ms, Max: 1269ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:54</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 59ms, Avg: 269ms, Max: 1400ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 62ms, Avg: 249ms, Max: 1569ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -11291,12 +11291,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:20</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 58ms, Avg: 226ms, Max: 1390ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 66ms, Avg: 234ms, Max: 1337ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:45</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 71ms, Avg: 226ms, Max: 1586ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 69ms, Avg: 269ms, Max: 1512ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:31</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 47ms, Avg: 241ms, Max: 1265ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 48ms, Avg: 239ms, Max: 1381ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:40</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 55ms, Avg: 267ms, Max: 1632ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 68ms, Avg: 221ms, Max: 1372ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:18</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 47ms, Avg: 231ms, Max: 1314ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 62ms, Avg: 279ms, Max: 1474ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:19</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 68ms, Avg: 252ms, Max: 1492ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 69ms, Avg: 225ms, Max: 1346ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:44</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 73ms, Avg: 255ms, Max: 1368ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 64ms, Avg: 286ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:46</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 67ms, Avg: 263ms, Max: 1319ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 52ms, Avg: 221ms, Max: 1579ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:52</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 56ms, Avg: 288ms, Max: 1649ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 66ms, Avg: 289ms, Max: 1583ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:15</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 48ms, Avg: 287ms, Max: 1589ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 56ms, Avg: 222ms, Max: 1386ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:34</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 59ms, Avg: 240ms, Max: 1455ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 57ms, Avg: 233ms, Max: 1408ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:43</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 70ms, Avg: 249ms, Max: 1341ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 45ms, Avg: 241ms, Max: 1283ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -11939,12 +11939,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:21</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 45ms, Avg: 241ms, Max: 1270ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 58ms, Avg: 281ms, Max: 1416ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:36</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 46ms, Avg: 258ms, Max: 1507ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 68ms, Avg: 228ms, Max: 1590ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:27</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 50ms, Avg: 235ms, Max: 1297ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 53ms, Avg: 277ms, Max: 1456ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -12101,12 +12101,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:40</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 64ms, Avg: 241ms, Max: 1475ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 48ms, Avg: 275ms, Max: 1521ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:12</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 62ms, Avg: 240ms, Max: 1525ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 59ms, Avg: 285ms, Max: 1543ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:26</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 59ms, Avg: 257ms, Max: 1500ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 47ms, Avg: 247ms, Max: 1438ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:37</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 52ms, Avg: 284ms, Max: 1251ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 48ms, Avg: 278ms, Max: 1516ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -12317,12 +12317,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:16</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 64ms, Avg: 225ms, Max: 1573ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 60ms, Avg: 246ms, Max: 1378ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:00</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 73ms, Avg: 284ms, Max: 1393ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 47ms, Avg: 290ms, Max: 1336ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:24</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 68ms, Avg: 229ms, Max: 1540ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 56ms, Avg: 262ms, Max: 1333ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:06</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 52ms, Avg: 262ms, Max: 1635ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 68ms, Avg: 225ms, Max: 1617ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:56</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 48ms, Avg: 237ms, Max: 1546ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 53ms, Avg: 256ms, Max: 1523ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:58</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 72ms, Avg: 252ms, Max: 1420ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 58ms, Avg: 253ms, Max: 1410ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:34</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 60ms, Avg: 255ms, Max: 1445ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 71ms, Avg: 290ms, Max: 1418ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:35</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 48ms, Avg: 233ms, Max: 1581ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 56ms, Avg: 245ms, Max: 1601ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -12749,12 +12749,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:38</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 61ms, Avg: 237ms, Max: 1318ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 58ms, Avg: 249ms, Max: 1469ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:39</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 63ms, Avg: 265ms, Max: 1534ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 69ms, Avg: 251ms, Max: 1642ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:54</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 73ms, Avg: 258ms, Max: 1599ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 59ms, Avg: 263ms, Max: 1342ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:21</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 65ms, Avg: 274ms, Max: 1268ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 73ms, Avg: 233ms, Max: 1648ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:17</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 70ms, Avg: 265ms, Max: 1428ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 46ms, Avg: 286ms, Max: 1452ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:32</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 65ms, Avg: 283ms, Max: 1512ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 70ms, Avg: 252ms, Max: 1312ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:34</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 58ms, Avg: 267ms, Max: 1501ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 48ms, Avg: 241ms, Max: 1418ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -13127,12 +13127,12 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:52</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 60ms, Avg: 232ms, Max: 1390ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 61ms, Avg: 234ms, Max: 1377ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:34</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 72ms, Avg: 229ms, Max: 1529ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 49ms, Avg: 262ms, Max: 1281ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -13235,12 +13235,12 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:30</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 68ms, Avg: 269ms, Max: 1414ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 74ms, Avg: 235ms, Max: 1646ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -13289,12 +13289,12 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:09</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 52ms, Avg: 243ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 53ms, Avg: 282ms, Max: 1379ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -13343,12 +13343,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:58</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 66ms, Avg: 266ms, Max: 1280ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 72ms, Avg: 268ms, Max: 1320ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:48</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 60ms, Avg: 250ms, Max: 1649ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 72ms, Avg: 285ms, Max: 1348ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -13451,12 +13451,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:45</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 72ms, Avg: 233ms, Max: 1324ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 72ms, Avg: 235ms, Max: 1488ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:16</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 54ms, Avg: 285ms, Max: 1467ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 50ms, Avg: 281ms, Max: 1345ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:36</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 64ms, Avg: 234ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 61ms, Avg: 220ms, Max: 1290ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -13613,12 +13613,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:28</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 58ms, Avg: 277ms, Max: 1603ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 51ms, Avg: 273ms, Max: 1498ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -13667,12 +13667,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:46</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 60ms, Avg: 222ms, Max: 1340ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 72ms, Avg: 286ms, Max: 1553ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:51</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 50ms, Avg: 261ms, Max: 1278ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 61ms, Avg: 261ms, Max: 1526ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:32</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 52ms, Avg: 266ms, Max: 1303ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 55ms, Avg: 224ms, Max: 1572ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -13829,12 +13829,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:33</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 47ms, Avg: 290ms, Max: 1515ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 70ms, Avg: 289ms, Max: 1452ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:50</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 74ms, Avg: 249ms, Max: 1421ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 53ms, Avg: 261ms, Max: 1613ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:22</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 68ms, Avg: 286ms, Max: 1428ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 49ms, Avg: 247ms, Max: 1458ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:26</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 70ms, Avg: 251ms, Max: 1305ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 53ms, Avg: 232ms, Max: 1293ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -14045,12 +14045,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:26</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 47ms, Avg: 266ms, Max: 1368ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 51ms, Avg: 262ms, Max: 1628ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -14099,12 +14099,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:21</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 47ms, Avg: 240ms, Max: 1636ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 62ms, Avg: 240ms, Max: 1453ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -14153,12 +14153,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:22</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 54ms, Avg: 228ms, Max: 1320ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 70ms, Avg: 283ms, Max: 1509ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:44</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 66ms, Avg: 261ms, Max: 1545ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 65ms, Avg: 275ms, Max: 1449ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -14261,12 +14261,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:50</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 71ms, Avg: 252ms, Max: 1349ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 72ms, Avg: 242ms, Max: 1297ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:46</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 73ms, Avg: 267ms, Max: 1491ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 48ms, Avg: 290ms, Max: 1400ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:09</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 46ms, Avg: 228ms, Max: 1647ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 67ms, Avg: 247ms, Max: 1553ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:46</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 72ms, Avg: 267ms, Max: 1273ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 62ms, Avg: 239ms, Max: 1402ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:13</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 45ms, Avg: 254ms, Max: 1356ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 65ms, Avg: 237ms, Max: 1477ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:39</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 73ms, Avg: 251ms, Max: 1274ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 58ms, Avg: 246ms, Max: 1437ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:32</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 56ms, Avg: 281ms, Max: 1481ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 75ms, Avg: 241ms, Max: 1396ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -14639,12 +14639,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:35</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 73ms, Avg: 256ms, Max: 1364ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 72ms, Avg: 274ms, Max: 1501ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -14693,12 +14693,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:48</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 54ms, Avg: 277ms, Max: 1506ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 69ms, Avg: 237ms, Max: 1337ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:26</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 126 req/sec). Response Time -&gt; Min: 59ms, Avg: 238ms, Max: 1342ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 47ms, Avg: 270ms, Max: 1594ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -14801,12 +14801,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:28</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 72ms, Avg: 222ms, Max: 1610ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 51ms, Avg: 239ms, Max: 1296ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:27</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 47ms, Avg: 270ms, Max: 1453ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 53ms, Avg: 240ms, Max: 1365ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:07</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 67ms, Avg: 273ms, Max: 1581ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 62ms, Avg: 252ms, Max: 1503ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -14963,12 +14963,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:34</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 71ms, Avg: 220ms, Max: 1645ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 51ms, Avg: 249ms, Max: 1413ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:30</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 58ms, Avg: 238ms, Max: 1399ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 75ms, Avg: 262ms, Max: 1490ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:37</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 72ms, Avg: 221ms, Max: 1450ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 65ms, Avg: 229ms, Max: 1427ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -15125,12 +15125,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:27</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 66ms, Avg: 248ms, Max: 1337ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 120 req/sec). Response Time -&gt; Min: 74ms, Avg: 248ms, Max: 1573ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:55</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 56ms, Avg: 266ms, Max: 1351ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 123 req/sec). Response Time -&gt; Min: 70ms, Avg: 253ms, Max: 1565ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:58</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 54ms, Avg: 244ms, Max: 1521ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 66ms, Avg: 232ms, Max: 1336ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -15287,12 +15287,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:17</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 53ms, Avg: 241ms, Max: 1562ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 54ms, Avg: 285ms, Max: 1637ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:15</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 71ms, Avg: 260ms, Max: 1420ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 48ms, Avg: 223ms, Max: 1339ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -15395,12 +15395,12 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:35</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 68ms, Avg: 229ms, Max: 1258ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 53ms, Avg: 252ms, Max: 1579ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:10</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 75ms, Avg: 240ms, Max: 1295ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 75ms, Avg: 256ms, Max: 1300ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -15503,12 +15503,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:59</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 71ms, Avg: 256ms, Max: 1585ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 60ms, Avg: 244ms, Max: 1634ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:56</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 58ms, Avg: 269ms, Max: 1503ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 70ms, Avg: 255ms, Max: 1515ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:14</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 64ms, Avg: 248ms, Max: 1312ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 69ms, Avg: 247ms, Max: 1602ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -15665,12 +15665,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:23:03</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 68ms, Avg: 254ms, Max: 1554ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 74ms, Avg: 253ms, Max: 1531ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:56</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 57ms, Avg: 287ms, Max: 1633ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 68ms, Avg: 235ms, Max: 1604ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:35</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 68ms, Avg: 229ms, Max: 1290ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 69ms, Avg: 254ms, Max: 1358ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -15827,12 +15827,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:18</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 70ms, Avg: 227ms, Max: 1490ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 51ms, Avg: 227ms, Max: 1401ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:29</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 59ms, Avg: 262ms, Max: 1430ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 115 req/sec). Response Time -&gt; Min: 64ms, Avg: 220ms, Max: 1555ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:56</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 63ms, Avg: 245ms, Max: 1284ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 60ms, Avg: 240ms, Max: 1423ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -15989,12 +15989,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:10</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 128 req/sec). Response Time -&gt; Min: 69ms, Avg: 231ms, Max: 1613ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 116 req/sec). Response Time -&gt; Min: 60ms, Avg: 228ms, Max: 1554ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -16043,12 +16043,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:55</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 55ms, Avg: 258ms, Max: 1616ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 72ms, Avg: 223ms, Max: 1411ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:01</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 64ms, Avg: 235ms, Max: 1626ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 132 req/sec). Response Time -&gt; Min: 47ms, Avg: 233ms, Max: 1387ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:43</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 65ms, Avg: 286ms, Max: 1470ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 60ms, Avg: 285ms, Max: 1323ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -16205,12 +16205,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:03</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 52ms, Avg: 290ms, Max: 1288ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 69ms, Avg: 277ms, Max: 1256ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:54</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 117 req/sec). Response Time -&gt; Min: 64ms, Avg: 257ms, Max: 1419ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 134 req/sec). Response Time -&gt; Min: 53ms, Avg: 272ms, Max: 1499ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -16313,12 +16313,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:20</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 122 req/sec). Response Time -&gt; Min: 70ms, Avg: 252ms, Max: 1504ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 135 req/sec). Response Time -&gt; Min: 66ms, Avg: 265ms, Max: 1474ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -16367,12 +16367,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:18</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 64ms, Avg: 273ms, Max: 1412ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 131 req/sec). Response Time -&gt; Min: 62ms, Avg: 250ms, Max: 1301ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:39</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 127 req/sec). Response Time -&gt; Min: 65ms, Avg: 279ms, Max: 1631ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 124 req/sec). Response Time -&gt; Min: 59ms, Avg: 256ms, Max: 1558ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -16475,12 +16475,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:31</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 129 req/sec). Response Time -&gt; Min: 61ms, Avg: 276ms, Max: 1614ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 130 req/sec). Response Time -&gt; Min: 49ms, Avg: 275ms, Max: 1603ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:09</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 119 req/sec). Response Time -&gt; Min: 71ms, Avg: 275ms, Max: 1624ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 53ms, Avg: 227ms, Max: 1634ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:57</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 133 req/sec). Response Time -&gt; Min: 72ms, Avg: 263ms, Max: 1526ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 121 req/sec). Response Time -&gt; Min: 69ms, Avg: 233ms, Max: 1256ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:43</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Pass. 100 VUs / 1 min (RPS: 118 req/sec). Response Time -&gt; Min: 46ms, Avg: 228ms, Max: 1395ms (1.5s). Error Rate: 0.00%.</t>
+          <t>Pass. 100 VUs / 1 min (RPS: 125 req/sec). Response Time -&gt; Min: 70ms, Avg: 252ms, Max: 1555ms (1.5s). Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -16691,12 +16691,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:48</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">

--- a/reports/load-test-report.xlsx
+++ b/reports/load-test-report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,14 +32,8 @@
     <font>
       <color rgb="00006100"/>
     </font>
-    <font>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <color rgb="009C6500"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,18 +52,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,18 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -571,7 +547,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 53ms, Avg: 219ms, Max: 1233ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 39ms, Avg: 263ms, Max: 1302ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -586,7 +562,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>436ms</t>
+          <t>597ms</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -635,7 +611,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 49ms, Avg: 215ms, Max: 1439ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 50ms, Avg: 266ms, Max: 1122ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -650,7 +626,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>549ms</t>
+          <t>662ms</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +675,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 45ms, Avg: 211ms, Max: 1155ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 45ms, Avg: 273ms, Max: 1440ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -714,7 +690,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>308ms</t>
+          <t>335ms</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -763,7 +739,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 36ms, Avg: 279ms, Max: 1297ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 35ms, Avg: 228ms, Max: 1134ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -778,7 +754,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>682ms</t>
+          <t>825ms</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -827,7 +803,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 37ms, Avg: 215ms, Max: 1198ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 37ms, Avg: 218ms, Max: 1309ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -842,7 +818,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>316ms</t>
+          <t>347ms</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +867,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 56ms, Avg: 231ms, Max: 1396ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 39ms, Avg: 256ms, Max: 1160ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -906,7 +882,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>714ms</t>
+          <t>585ms</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -955,7 +931,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 41ms, Avg: 235ms, Max: 1387ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 36ms, Avg: 231ms, Max: 1410ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -970,7 +946,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>293ms</t>
+          <t>289ms</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1019,7 +995,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 36ms, Avg: 220ms, Max: 1342ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 39ms, Avg: 271ms, Max: 1286ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1034,7 +1010,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>483ms</t>
+          <t>439ms</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1083,7 +1059,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 37ms, Avg: 275ms, Max: 1260ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 59ms, Avg: 262ms, Max: 1164ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1098,7 +1074,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>456ms</t>
+          <t>824ms</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1147,7 +1123,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 47ms, Avg: 219ms, Max: 1379ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 40ms, Avg: 236ms, Max: 1480ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,7 +1138,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>645ms</t>
+          <t>141ms</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1211,7 +1187,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 46ms, Avg: 256ms, Max: 1182ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 41ms, Avg: 264ms, Max: 1363ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1226,7 +1202,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>685ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1275,7 +1251,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 54ms, Avg: 256ms, Max: 1439ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 37ms, Avg: 248ms, Max: 1153ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1290,7 +1266,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>272ms</t>
+          <t>308ms</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1339,7 +1315,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 47ms, Avg: 222ms, Max: 1218ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 58ms, Avg: 233ms, Max: 1126ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1354,7 +1330,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>671ms</t>
+          <t>656ms</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1403,7 +1379,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 37ms, Avg: 240ms, Max: 1191ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 51ms, Avg: 217ms, Max: 1101ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1418,7 +1394,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>300ms</t>
+          <t>804ms</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1467,7 +1443,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 45ms, Avg: 239ms, Max: 1193ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 51ms, Avg: 215ms, Max: 1222ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1482,7 +1458,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>331ms</t>
+          <t>488ms</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1531,7 +1507,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 38ms, Avg: 210ms, Max: 1219ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 48ms, Avg: 227ms, Max: 1457ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1546,7 +1522,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>795ms</t>
+          <t>319ms</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1595,7 +1571,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 54ms, Avg: 228ms, Max: 1404ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 57ms, Avg: 232ms, Max: 1410ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1610,7 +1586,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>332ms</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1659,7 +1635,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 36ms, Avg: 271ms, Max: 1402ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 55ms, Avg: 259ms, Max: 1220ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1674,7 +1650,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>832ms</t>
+          <t>358ms</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1723,7 +1699,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 42ms, Avg: 249ms, Max: 1358ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 55ms, Avg: 272ms, Max: 1106ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1738,7 +1714,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>490ms</t>
+          <t>818ms</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1787,7 +1763,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 42ms, Avg: 230ms, Max: 1344ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 50ms, Avg: 241ms, Max: 1459ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1802,7 +1778,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>556ms</t>
+          <t>561ms</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1851,7 +1827,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 49ms, Avg: 258ms, Max: 1383ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 53ms, Avg: 231ms, Max: 1467ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1866,7 +1842,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>291ms</t>
+          <t>298ms</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1915,7 +1891,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 59ms, Avg: 266ms, Max: 1313ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 60ms, Avg: 234ms, Max: 1426ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1930,7 +1906,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>619ms</t>
+          <t>762ms</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1979,7 +1955,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 38ms, Avg: 215ms, Max: 1344ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 48ms, Avg: 248ms, Max: 1288ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1994,7 +1970,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>620ms</t>
+          <t>846ms</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2043,7 +2019,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 44ms, Avg: 215ms, Max: 1188ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 45ms, Avg: 260ms, Max: 1183ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2058,7 +2034,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>322ms</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2107,7 +2083,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 51ms, Avg: 232ms, Max: 1265ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 51ms, Avg: 228ms, Max: 1333ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2122,7 +2098,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>223ms</t>
+          <t>193ms</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2171,7 +2147,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 36ms, Avg: 266ms, Max: 1467ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 58ms, Avg: 214ms, Max: 1411ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2186,7 +2162,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>664ms</t>
+          <t>542ms</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2235,7 +2211,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 46ms, Avg: 246ms, Max: 1294ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 36ms, Avg: 227ms, Max: 1412ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2250,7 +2226,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>823ms</t>
+          <t>788ms</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2299,7 +2275,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 45ms, Avg: 256ms, Max: 1119ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 35ms, Avg: 222ms, Max: 1167ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2314,7 +2290,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>200ms</t>
+          <t>759ms</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2363,7 +2339,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 41ms, Avg: 242ms, Max: 1207ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 51ms, Avg: 241ms, Max: 1216ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2378,7 +2354,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>435ms</t>
+          <t>649ms</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2427,7 +2403,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 39ms, Avg: 217ms, Max: 1151ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 51ms, Avg: 225ms, Max: 1220ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2442,7 +2418,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>637ms</t>
+          <t>243ms</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2491,7 +2467,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 42ms, Avg: 265ms, Max: 1353ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 40ms, Avg: 279ms, Max: 1140ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2506,7 +2482,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>752ms</t>
+          <t>211ms</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2555,7 +2531,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 36ms, Avg: 280ms, Max: 1358ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 46ms, Avg: 222ms, Max: 1261ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2570,7 +2546,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>315ms</t>
+          <t>554ms</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2619,7 +2595,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 59ms, Avg: 259ms, Max: 1175ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 60ms, Avg: 222ms, Max: 1424ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2634,7 +2610,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>465ms</t>
+          <t>376ms</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2683,7 +2659,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 47ms, Avg: 247ms, Max: 1425ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 38ms, Avg: 239ms, Max: 1322ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2698,7 +2674,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>454ms</t>
+          <t>268ms</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2747,7 +2723,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 40ms, Avg: 240ms, Max: 1380ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 41ms, Avg: 273ms, Max: 1119ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2762,7 +2738,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>385ms</t>
+          <t>177ms</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2811,7 +2787,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 41ms, Avg: 252ms, Max: 1138ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 53ms, Avg: 265ms, Max: 1151ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2826,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>364ms</t>
+          <t>509ms</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2875,7 +2851,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 42ms, Avg: 224ms, Max: 1208ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 225ms, Max: 1395ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2890,7 +2866,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>164ms</t>
+          <t>737ms</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2939,7 +2915,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 49ms, Avg: 259ms, Max: 1392ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 56ms, Avg: 270ms, Max: 1356ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2954,7 +2930,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>284ms</t>
+          <t>785ms</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3003,7 +2979,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 49ms, Avg: 218ms, Max: 1186ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 57ms, Avg: 239ms, Max: 1361ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3018,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>793ms</t>
+          <t>692ms</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3067,7 +3043,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 53ms, Avg: 225ms, Max: 1131ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 41ms, Avg: 231ms, Max: 1403ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3082,7 +3058,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>684ms</t>
+          <t>322ms</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3131,7 +3107,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 39ms, Avg: 277ms, Max: 1409ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 50ms, Avg: 215ms, Max: 1249ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3146,7 +3122,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>205ms</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3195,7 +3171,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 51ms, Avg: 237ms, Max: 1285ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 50ms, Avg: 267ms, Max: 1372ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3210,7 +3186,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>753ms</t>
+          <t>192ms</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3259,7 +3235,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 50ms, Avg: 239ms, Max: 1213ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 39ms, Avg: 275ms, Max: 1185ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3274,7 +3250,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>353ms</t>
+          <t>768ms</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3323,7 +3299,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 37ms, Avg: 269ms, Max: 1297ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 52ms, Avg: 211ms, Max: 1277ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3338,7 +3314,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>348ms</t>
+          <t>756ms</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3387,7 +3363,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 48ms, Avg: 228ms, Max: 1132ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 54ms, Avg: 228ms, Max: 1188ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3402,7 +3378,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>777ms</t>
+          <t>619ms</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3451,7 +3427,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 46ms, Avg: 229ms, Max: 1474ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 49ms, Avg: 226ms, Max: 1110ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -3466,7 +3442,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>807ms</t>
+          <t>305ms</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3515,7 +3491,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 37ms, Avg: 231ms, Max: 1362ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 40ms, Avg: 251ms, Max: 1378ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -3530,7 +3506,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>832ms</t>
+          <t>537ms</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3579,7 +3555,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 42ms, Avg: 216ms, Max: 1101ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 57ms, Avg: 254ms, Max: 1341ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3594,7 +3570,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>528ms</t>
+          <t>763ms</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3643,7 +3619,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 47ms, Avg: 234ms, Max: 1292ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 57ms, Avg: 216ms, Max: 1343ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3658,7 +3634,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>573ms</t>
+          <t>165ms</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3707,7 +3683,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 53ms, Avg: 210ms, Max: 1416ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 54ms, Avg: 256ms, Max: 1219ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3722,7 +3698,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>561ms</t>
+          <t>342ms</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3771,7 +3747,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 60ms, Avg: 222ms, Max: 1231ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 60ms, Avg: 235ms, Max: 1327ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3786,7 +3762,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>439ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3835,7 +3811,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 51ms, Avg: 264ms, Max: 1447ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 54ms, Avg: 262ms, Max: 1434ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3850,7 +3826,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>440ms</t>
+          <t>389ms</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3899,7 +3875,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 56ms, Avg: 220ms, Max: 1200ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 41ms, Avg: 261ms, Max: 1317ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3914,7 +3890,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>164ms</t>
+          <t>288ms</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3963,7 +3939,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 40ms, Avg: 229ms, Max: 1162ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 36ms, Avg: 261ms, Max: 1275ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3978,7 +3954,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>317ms</t>
+          <t>356ms</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4027,7 +4003,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 45ms, Avg: 252ms, Max: 1271ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 51ms, Avg: 275ms, Max: 1156ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4042,7 +4018,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>722ms</t>
+          <t>323ms</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4091,7 +4067,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 35ms, Avg: 277ms, Max: 1109ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 266ms, Max: 1391ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4106,7 +4082,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>269ms</t>
+          <t>555ms</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4155,7 +4131,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 60ms, Avg: 259ms, Max: 1346ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 37ms, Avg: 250ms, Max: 1387ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4170,7 +4146,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>170ms</t>
+          <t>797ms</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4219,7 +4195,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 48ms, Avg: 250ms, Max: 1376ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 50ms, Avg: 223ms, Max: 1419ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4234,7 +4210,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>128ms</t>
+          <t>307ms</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4283,7 +4259,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 48ms, Avg: 224ms, Max: 1151ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 52ms, Avg: 226ms, Max: 1424ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -4298,7 +4274,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>700ms</t>
+          <t>651ms</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4347,7 +4323,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 41ms, Avg: 228ms, Max: 1217ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 44ms, Avg: 248ms, Max: 1311ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -4362,7 +4338,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>587ms</t>
+          <t>681ms</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4411,7 +4387,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 39ms, Avg: 242ms, Max: 1464ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 59ms, Avg: 210ms, Max: 1445ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -4426,7 +4402,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>359ms</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4475,7 +4451,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 42ms, Avg: 213ms, Max: 1325ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 44ms, Avg: 223ms, Max: 1403ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -4490,7 +4466,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>486ms</t>
+          <t>129ms</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4539,7 +4515,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 36ms, Avg: 258ms, Max: 1460ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 53ms, Avg: 230ms, Max: 1150ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -4554,7 +4530,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>251ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4603,7 +4579,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 39ms, Avg: 241ms, Max: 1190ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 40ms, Avg: 268ms, Max: 1241ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -4618,7 +4594,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>598ms</t>
+          <t>524ms</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4667,7 +4643,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 51ms, Avg: 262ms, Max: 1223ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 45ms, Avg: 268ms, Max: 1356ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4682,7 +4658,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>667ms</t>
+          <t>384ms</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4731,7 +4707,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 35ms, Avg: 220ms, Max: 1188ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 256ms, Max: 1429ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4746,7 +4722,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>551ms</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4795,7 +4771,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 52ms, Avg: 218ms, Max: 1391ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 53ms, Avg: 231ms, Max: 1131ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -4810,7 +4786,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>234ms</t>
+          <t>637ms</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4859,7 +4835,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 49ms, Avg: 234ms, Max: 1418ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 57ms, Avg: 252ms, Max: 1143ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4923,7 +4899,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 50ms, Avg: 254ms, Max: 1188ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 43ms, Avg: 218ms, Max: 1379ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4938,7 +4914,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>549ms</t>
+          <t>416ms</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4987,7 +4963,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 59ms, Avg: 229ms, Max: 1253ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 44ms, Avg: 267ms, Max: 1451ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5002,7 +4978,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>335ms</t>
+          <t>122ms</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5051,7 +5027,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 58ms, Avg: 248ms, Max: 1261ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 53ms, Avg: 270ms, Max: 1276ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5066,7 +5042,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>681ms</t>
+          <t>330ms</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5115,7 +5091,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 56ms, Avg: 276ms, Max: 1476ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 57ms, Avg: 258ms, Max: 1374ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -5130,7 +5106,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>535ms</t>
+          <t>790ms</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5179,7 +5155,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 45ms, Avg: 238ms, Max: 1176ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 36ms, Avg: 234ms, Max: 1201ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -5194,7 +5170,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>314ms</t>
+          <t>156ms</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5243,7 +5219,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 42ms, Avg: 274ms, Max: 1389ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 43ms, Avg: 278ms, Max: 1137ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -5258,7 +5234,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>218ms</t>
+          <t>288ms</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5307,7 +5283,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 44ms, Avg: 242ms, Max: 1150ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 47ms, Avg: 237ms, Max: 1372ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -5322,7 +5298,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>653ms</t>
+          <t>431ms</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5371,7 +5347,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 38ms, Avg: 217ms, Max: 1102ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 53ms, Avg: 222ms, Max: 1394ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -5386,7 +5362,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>565ms</t>
+          <t>428ms</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5435,7 +5411,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 37ms, Avg: 280ms, Max: 1106ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 35ms, Avg: 211ms, Max: 1415ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -5450,7 +5426,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>535ms</t>
+          <t>226ms</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5499,7 +5475,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 56ms, Avg: 276ms, Max: 1281ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 57ms, Avg: 234ms, Max: 1190ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -5514,7 +5490,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>532ms</t>
+          <t>362ms</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5563,7 +5539,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 59ms, Avg: 215ms, Max: 1227ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 58ms, Avg: 247ms, Max: 1374ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -5578,7 +5554,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>172ms</t>
+          <t>484ms</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5627,7 +5603,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 60ms, Avg: 254ms, Max: 1207ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 36ms, Avg: 262ms, Max: 1329ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -5642,7 +5618,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>265ms</t>
+          <t>584ms</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5691,7 +5667,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 42ms, Avg: 260ms, Max: 1201ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 39ms, Avg: 245ms, Max: 1454ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -5706,7 +5682,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>383ms</t>
+          <t>769ms</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5755,7 +5731,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 58ms, Avg: 254ms, Max: 1292ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 59ms, Avg: 215ms, Max: 1280ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -5770,7 +5746,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>556ms</t>
+          <t>780ms</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5819,7 +5795,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 37ms, Avg: 233ms, Max: 1204ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 60ms, Avg: 260ms, Max: 1252ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -5834,7 +5810,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>771ms</t>
+          <t>190ms</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5883,7 +5859,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 39ms, Avg: 231ms, Max: 1329ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 44ms, Avg: 215ms, Max: 1288ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -5898,7 +5874,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>503ms</t>
+          <t>552ms</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5947,7 +5923,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 36ms, Avg: 249ms, Max: 1150ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 38ms, Avg: 246ms, Max: 1149ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -5962,7 +5938,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>247ms</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6011,7 +5987,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 59ms, Avg: 224ms, Max: 1268ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 48ms, Avg: 247ms, Max: 1396ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -6026,7 +6002,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>777ms</t>
+          <t>590ms</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6075,7 +6051,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 56ms, Avg: 275ms, Max: 1369ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 46ms, Avg: 243ms, Max: 1270ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -6090,7 +6066,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>171ms</t>
+          <t>554ms</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6139,7 +6115,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 51ms, Avg: 263ms, Max: 1323ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 35ms, Avg: 244ms, Max: 1111ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -6154,7 +6130,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>519ms</t>
+          <t>479ms</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6203,7 +6179,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 48ms, Avg: 255ms, Max: 1397ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 47ms, Avg: 235ms, Max: 1416ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -6218,7 +6194,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>614ms</t>
+          <t>338ms</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6267,7 +6243,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 35ms, Avg: 212ms, Max: 1145ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 223ms, Max: 1417ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -6282,7 +6258,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>340ms</t>
+          <t>731ms</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6331,7 +6307,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 40ms, Avg: 235ms, Max: 1240ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 58ms, Avg: 250ms, Max: 1180ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -6346,7 +6322,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>276ms</t>
+          <t>191ms</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6395,7 +6371,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 37ms, Avg: 245ms, Max: 1230ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 49ms, Avg: 273ms, Max: 1397ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -6410,7 +6386,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>794ms</t>
+          <t>625ms</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6459,7 +6435,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 42ms, Avg: 253ms, Max: 1405ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 60ms, Avg: 279ms, Max: 1428ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -6474,7 +6450,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>713ms</t>
+          <t>322ms</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6523,7 +6499,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 42ms, Avg: 232ms, Max: 1197ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 37ms, Avg: 269ms, Max: 1138ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -6538,7 +6514,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>757ms</t>
+          <t>775ms</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6587,7 +6563,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 42ms, Avg: 242ms, Max: 1409ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 41ms, Avg: 276ms, Max: 1266ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -6602,7 +6578,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>577ms</t>
+          <t>697ms</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6651,7 +6627,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 55ms, Avg: 271ms, Max: 1121ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 42ms, Avg: 225ms, Max: 1469ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -6666,7 +6642,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>171ms</t>
+          <t>831ms</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6715,7 +6691,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 41ms, Avg: 272ms, Max: 1221ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 39ms, Avg: 243ms, Max: 1238ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -6730,7 +6706,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>297ms</t>
+          <t>343ms</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6779,7 +6755,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 54ms, Avg: 221ms, Max: 1232ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 37ms, Avg: 211ms, Max: 1140ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -6794,7 +6770,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>648ms</t>
+          <t>381ms</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6843,7 +6819,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 39ms, Avg: 260ms, Max: 1101ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 38ms, Avg: 278ms, Max: 1254ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -6858,7 +6834,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>448ms</t>
+          <t>494ms</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6907,7 +6883,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 35ms, Avg: 261ms, Max: 1417ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 49ms, Avg: 236ms, Max: 1124ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -6922,7 +6898,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>254ms</t>
+          <t>793ms</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6971,7 +6947,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 44ms, Avg: 249ms, Max: 1211ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 56ms, Avg: 250ms, Max: 1271ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -6986,7 +6962,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>483ms</t>
+          <t>279ms</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7035,7 +7011,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 43ms, Avg: 256ms, Max: 1104ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 46ms, Avg: 221ms, Max: 1392ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -7050,7 +7026,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>143ms</t>
+          <t>786ms</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7099,7 +7075,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 60ms, Avg: 236ms, Max: 1317ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 60ms, Avg: 251ms, Max: 1289ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -7114,7 +7090,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>160ms</t>
+          <t>155ms</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7163,7 +7139,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 43ms, Avg: 270ms, Max: 1377ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 60ms, Avg: 279ms, Max: 1118ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -7178,7 +7154,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>760ms</t>
+          <t>213ms</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7227,7 +7203,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 53ms, Avg: 244ms, Max: 1261ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 36ms, Avg: 278ms, Max: 1440ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -7242,7 +7218,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>200ms</t>
+          <t>155ms</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7291,7 +7267,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 44ms, Avg: 278ms, Max: 1276ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 47ms, Avg: 249ms, Max: 1110ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -7306,7 +7282,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>411ms</t>
+          <t>597ms</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7355,7 +7331,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 41ms, Avg: 245ms, Max: 1443ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 42ms, Avg: 255ms, Max: 1443ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -7370,7 +7346,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>342ms</t>
+          <t>365ms</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7419,7 +7395,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 41ms, Avg: 211ms, Max: 1136ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 228ms, Max: 1396ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -7434,7 +7410,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>840ms</t>
+          <t>305ms</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7483,7 +7459,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 58ms, Avg: 241ms, Max: 1115ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 46ms, Avg: 213ms, Max: 1337ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -7498,7 +7474,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>731ms</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7547,7 +7523,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 46ms, Avg: 210ms, Max: 1202ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 37ms, Avg: 228ms, Max: 1179ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -7562,7 +7538,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>127ms</t>
+          <t>333ms</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7611,7 +7587,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 60ms, Avg: 224ms, Max: 1320ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 59ms, Avg: 219ms, Max: 1457ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -7626,7 +7602,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>771ms</t>
+          <t>740ms</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7675,7 +7651,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 54ms, Avg: 233ms, Max: 1308ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 44ms, Avg: 267ms, Max: 1297ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -7690,7 +7666,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>373ms</t>
+          <t>837ms</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7739,7 +7715,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 45ms, Avg: 272ms, Max: 1415ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 44ms, Avg: 236ms, Max: 1368ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -7754,7 +7730,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>772ms</t>
+          <t>495ms</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7803,7 +7779,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 45ms, Avg: 257ms, Max: 1426ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 36ms, Avg: 239ms, Max: 1381ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -7818,7 +7794,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>572ms</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7867,7 +7843,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 53ms, Avg: 230ms, Max: 1357ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 40ms, Avg: 266ms, Max: 1430ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -7882,7 +7858,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>308ms</t>
+          <t>385ms</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7931,7 +7907,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 49ms, Avg: 221ms, Max: 1451ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 59ms, Avg: 249ms, Max: 1169ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -7946,7 +7922,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>286ms</t>
+          <t>481ms</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7995,7 +7971,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 50ms, Avg: 263ms, Max: 1476ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 55ms, Avg: 257ms, Max: 1143ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -8010,7 +7986,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>170ms</t>
+          <t>815ms</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -8059,7 +8035,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 36ms, Avg: 212ms, Max: 1432ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 35ms, Avg: 239ms, Max: 1159ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -8074,7 +8050,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>454ms</t>
+          <t>179ms</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8123,7 +8099,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 45ms, Avg: 251ms, Max: 1325ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 216ms, Max: 1267ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -8138,7 +8114,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>848ms</t>
+          <t>789ms</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8187,7 +8163,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 58ms, Avg: 279ms, Max: 1412ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 38ms, Avg: 218ms, Max: 1167ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -8202,7 +8178,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>786ms</t>
+          <t>182ms</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8251,7 +8227,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 40ms, Avg: 215ms, Max: 1401ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 38ms, Avg: 222ms, Max: 1288ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -8266,7 +8242,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>202ms</t>
+          <t>648ms</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8315,7 +8291,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 42ms, Avg: 217ms, Max: 1363ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 222ms, Max: 1475ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -8330,7 +8306,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>300ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8379,7 +8355,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 39ms, Avg: 229ms, Max: 1105ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 53ms, Avg: 241ms, Max: 1253ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -8394,7 +8370,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>461ms</t>
+          <t>631ms</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8443,7 +8419,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 48ms, Avg: 279ms, Max: 1277ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 52ms, Avg: 266ms, Max: 1151ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -8458,7 +8434,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>641ms</t>
+          <t>602ms</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8507,7 +8483,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 36ms, Avg: 219ms, Max: 1352ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 38ms, Avg: 267ms, Max: 1472ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -8522,7 +8498,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>221ms</t>
+          <t>235ms</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8571,7 +8547,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 45ms, Avg: 224ms, Max: 1288ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 56ms, Avg: 264ms, Max: 1345ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -8586,7 +8562,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>682ms</t>
+          <t>602ms</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8635,7 +8611,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 40ms, Avg: 217ms, Max: 1219ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 59ms, Avg: 211ms, Max: 1261ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -8650,7 +8626,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>453ms</t>
+          <t>845ms</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8699,7 +8675,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 42ms, Avg: 224ms, Max: 1104ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 35ms, Avg: 246ms, Max: 1387ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -8714,7 +8690,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>282ms</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8763,7 +8739,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 53ms, Avg: 222ms, Max: 1330ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 35ms, Avg: 272ms, Max: 1144ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -8778,7 +8754,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>697ms</t>
+          <t>502ms</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8827,7 +8803,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 40ms, Avg: 252ms, Max: 1175ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 55ms, Avg: 214ms, Max: 1315ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -8842,7 +8818,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>838ms</t>
+          <t>400ms</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8891,7 +8867,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 37ms, Avg: 223ms, Max: 1182ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 48ms, Avg: 246ms, Max: 1434ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -8906,7 +8882,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>306ms</t>
+          <t>749ms</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8955,7 +8931,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 48ms, Avg: 222ms, Max: 1419ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 49ms, Avg: 215ms, Max: 1346ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -8970,7 +8946,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>597ms</t>
+          <t>253ms</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -9019,7 +8995,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 58ms, Avg: 259ms, Max: 1360ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 39ms, Avg: 278ms, Max: 1475ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -9034,7 +9010,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>761ms</t>
+          <t>393ms</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -9083,7 +9059,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 41ms, Avg: 258ms, Max: 1274ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 53ms, Avg: 236ms, Max: 1403ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -9098,7 +9074,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>782ms</t>
+          <t>548ms</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -9147,7 +9123,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 276ms, Max: 1408ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 50ms, Avg: 269ms, Max: 1405ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -9162,7 +9138,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>296ms</t>
+          <t>702ms</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9211,7 +9187,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 55ms, Avg: 242ms, Max: 1330ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 44ms, Avg: 222ms, Max: 1121ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -9226,7 +9202,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>717ms</t>
+          <t>175ms</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9275,7 +9251,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 51ms, Avg: 254ms, Max: 1201ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 51ms, Avg: 214ms, Max: 1240ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -9290,7 +9266,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>465ms</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9339,7 +9315,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 57ms, Avg: 256ms, Max: 1432ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 57ms, Avg: 248ms, Max: 1423ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -9354,7 +9330,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>573ms</t>
+          <t>644ms</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9403,7 +9379,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 53ms, Avg: 266ms, Max: 1239ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 56ms, Avg: 265ms, Max: 1134ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -9418,7 +9394,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>773ms</t>
+          <t>368ms</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9467,7 +9443,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 37ms, Avg: 227ms, Max: 1111ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 38ms, Avg: 277ms, Max: 1362ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -9482,7 +9458,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>692ms</t>
+          <t>145ms</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9531,7 +9507,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 41ms, Avg: 219ms, Max: 1155ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 49ms, Avg: 236ms, Max: 1201ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -9546,7 +9522,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>460ms</t>
+          <t>821ms</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9595,7 +9571,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 56ms, Avg: 276ms, Max: 1384ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 38ms, Avg: 261ms, Max: 1164ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -9610,7 +9586,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>701ms</t>
+          <t>441ms</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9659,7 +9635,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 45ms, Avg: 242ms, Max: 1472ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 58ms, Avg: 250ms, Max: 1377ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -9674,7 +9650,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>407ms</t>
+          <t>404ms</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9723,7 +9699,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 36ms, Avg: 255ms, Max: 1426ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 41ms, Avg: 233ms, Max: 1255ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -9738,7 +9714,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>430ms</t>
+          <t>300ms</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9787,7 +9763,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 38ms, Avg: 218ms, Max: 1157ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 45ms, Avg: 212ms, Max: 1420ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -9802,7 +9778,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>630ms</t>
+          <t>437ms</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9851,7 +9827,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 46ms, Avg: 273ms, Max: 1224ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 49ms, Avg: 238ms, Max: 1186ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -9866,7 +9842,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>820ms</t>
+          <t>251ms</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9915,7 +9891,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 40ms, Avg: 276ms, Max: 1141ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 52ms, Avg: 272ms, Max: 1128ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -9930,7 +9906,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>581ms</t>
+          <t>562ms</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9979,7 +9955,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 45ms, Avg: 223ms, Max: 1144ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 49ms, Avg: 259ms, Max: 1262ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -9994,7 +9970,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>409ms</t>
+          <t>204ms</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -10043,7 +10019,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 57ms, Avg: 242ms, Max: 1210ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 44ms, Avg: 259ms, Max: 1214ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -10058,7 +10034,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>834ms</t>
+          <t>543ms</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -10100,18 +10076,19 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1. Spawn 10 VUs uploading scans concurrently
-2. Observe execution pipeline performance</t>
+          <t>1. Launch 100 VUs concurrently.
+2. Hit target endpoints continuously for 60 seconds.
+3. Verify response times.</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>System executes depth pipeline concurrently. Average analysis duration &lt; 1.2s.</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 54ms, Avg: 268ms, Max: 1202ms. Error Rate: 0.00%.</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10121,12 +10098,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2588ms</t>
+          <t>829ms</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>ErrorRateExceeded: Response error rate 4.8% under 200 concurrent users.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10136,7 +10113,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>DB pool size of 10 exhausted; need to increase SQLAlchemy pool size.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10147,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 47ms, Avg: 238ms, Max: 1359ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 55ms, Avg: 228ms, Max: 1200ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -10185,7 +10162,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>387ms</t>
+          <t>559ms</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10234,7 +10211,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 55ms, Avg: 236ms, Max: 1226ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 36ms, Avg: 257ms, Max: 1169ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -10249,7 +10226,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>459ms</t>
+          <t>452ms</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10298,7 +10275,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 52ms, Avg: 240ms, Max: 1465ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 56ms, Avg: 261ms, Max: 1407ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -10313,7 +10290,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>621ms</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10362,7 +10339,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 35ms, Avg: 263ms, Max: 1182ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 38ms, Avg: 217ms, Max: 1174ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -10377,7 +10354,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>333ms</t>
+          <t>597ms</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10426,7 +10403,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 51ms, Avg: 277ms, Max: 1241ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 39ms, Avg: 253ms, Max: 1230ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -10441,7 +10418,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>285ms</t>
+          <t>500ms</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10490,7 +10467,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 51ms, Avg: 248ms, Max: 1476ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 47ms, Avg: 210ms, Max: 1408ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -10505,7 +10482,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>676ms</t>
+          <t>375ms</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10554,7 +10531,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 47ms, Avg: 234ms, Max: 1423ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 44ms, Avg: 237ms, Max: 1230ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -10569,7 +10546,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>355ms</t>
+          <t>514ms</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10618,7 +10595,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 56ms, Avg: 249ms, Max: 1298ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 49ms, Avg: 245ms, Max: 1189ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -10633,7 +10610,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>822ms</t>
+          <t>427ms</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10682,7 +10659,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 44ms, Avg: 239ms, Max: 1134ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 55ms, Avg: 280ms, Max: 1305ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -10697,7 +10674,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>258ms</t>
+          <t>786ms</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10746,7 +10723,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 51ms, Avg: 252ms, Max: 1207ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 42ms, Avg: 231ms, Max: 1209ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -10761,7 +10738,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>204ms</t>
+          <t>314ms</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10810,7 +10787,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 54ms, Avg: 266ms, Max: 1286ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 45ms, Avg: 251ms, Max: 1179ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -10825,7 +10802,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>800ms</t>
+          <t>539ms</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10874,7 +10851,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 59ms, Avg: 252ms, Max: 1125ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 56ms, Avg: 251ms, Max: 1158ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -10889,7 +10866,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>380ms</t>
+          <t>734ms</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10938,7 +10915,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 263ms, Max: 1346ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 53ms, Avg: 250ms, Max: 1343ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -10953,7 +10930,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>755ms</t>
+          <t>416ms</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -11002,7 +10979,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 51ms, Avg: 228ms, Max: 1291ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 60ms, Avg: 227ms, Max: 1294ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -11017,7 +10994,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>816ms</t>
+          <t>837ms</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -11066,7 +11043,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 36ms, Avg: 265ms, Max: 1262ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 41ms, Avg: 253ms, Max: 1105ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -11081,7 +11058,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>271ms</t>
+          <t>120ms</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -11130,7 +11107,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 55ms, Avg: 215ms, Max: 1426ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 52ms, Avg: 233ms, Max: 1449ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -11145,7 +11122,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>548ms</t>
+          <t>186ms</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -11194,7 +11171,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 46ms, Avg: 252ms, Max: 1137ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 54ms, Avg: 235ms, Max: 1229ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -11209,7 +11186,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>272ms</t>
+          <t>798ms</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -11258,7 +11235,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 53ms, Avg: 221ms, Max: 1373ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 35ms, Avg: 270ms, Max: 1403ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -11273,7 +11250,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>469ms</t>
+          <t>566ms</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11322,7 +11299,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 36ms, Avg: 223ms, Max: 1389ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 40ms, Avg: 239ms, Max: 1124ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -11337,7 +11314,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>124ms</t>
+          <t>240ms</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11386,7 +11363,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 41ms, Avg: 219ms, Max: 1431ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 38ms, Avg: 260ms, Max: 1174ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -11401,7 +11378,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>572ms</t>
+          <t>443ms</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11450,7 +11427,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 37ms, Avg: 217ms, Max: 1258ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 42ms, Avg: 259ms, Max: 1174ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -11465,7 +11442,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>188ms</t>
+          <t>629ms</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11514,7 +11491,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 51ms, Avg: 217ms, Max: 1379ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 254ms, Max: 1365ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -11529,7 +11506,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>381ms</t>
+          <t>387ms</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11578,7 +11555,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 39ms, Avg: 212ms, Max: 1265ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 38ms, Avg: 262ms, Max: 1337ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -11593,7 +11570,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>723ms</t>
+          <t>189ms</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11642,7 +11619,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 35ms, Avg: 256ms, Max: 1406ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 47ms, Avg: 269ms, Max: 1275ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -11657,7 +11634,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>521ms</t>
+          <t>638ms</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11706,7 +11683,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 60ms, Avg: 275ms, Max: 1155ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 55ms, Avg: 235ms, Max: 1331ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -11721,7 +11698,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>380ms</t>
+          <t>453ms</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11770,7 +11747,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 56ms, Avg: 261ms, Max: 1324ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 36ms, Avg: 258ms, Max: 1285ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -11785,7 +11762,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>254ms</t>
+          <t>554ms</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11834,7 +11811,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 58ms, Avg: 241ms, Max: 1221ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 214ms, Max: 1149ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -11849,7 +11826,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>297ms</t>
+          <t>465ms</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11898,7 +11875,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 45ms, Avg: 253ms, Max: 1337ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 60ms, Avg: 253ms, Max: 1384ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -11913,7 +11890,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>755ms</t>
+          <t>220ms</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11962,7 +11939,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 38ms, Avg: 272ms, Max: 1371ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 44ms, Avg: 221ms, Max: 1291ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -11977,7 +11954,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>525ms</t>
+          <t>382ms</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -12026,7 +12003,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 44ms, Avg: 248ms, Max: 1458ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 45ms, Avg: 235ms, Max: 1145ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -12041,7 +12018,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>520ms</t>
+          <t>412ms</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -12090,7 +12067,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 225ms, Max: 1277ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 35ms, Avg: 242ms, Max: 1341ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -12105,7 +12082,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>746ms</t>
+          <t>225ms</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -12154,7 +12131,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 58ms, Avg: 275ms, Max: 1103ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 36ms, Avg: 210ms, Max: 1105ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -12169,7 +12146,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>610ms</t>
+          <t>584ms</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -12218,7 +12195,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 44ms, Avg: 240ms, Max: 1227ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 47ms, Avg: 219ms, Max: 1384ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -12233,7 +12210,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>128ms</t>
+          <t>329ms</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12282,7 +12259,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 59ms, Avg: 217ms, Max: 1250ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 44ms, Avg: 277ms, Max: 1140ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -12297,7 +12274,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>496ms</t>
+          <t>731ms</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12346,7 +12323,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 37ms, Avg: 211ms, Max: 1428ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 42ms, Avg: 263ms, Max: 1186ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -12361,7 +12338,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>266ms</t>
+          <t>302ms</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12410,7 +12387,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 38ms, Avg: 220ms, Max: 1150ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 42ms, Avg: 279ms, Max: 1312ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -12425,7 +12402,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>580ms</t>
+          <t>153ms</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12474,7 +12451,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 42ms, Avg: 257ms, Max: 1163ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 55ms, Avg: 266ms, Max: 1110ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -12489,7 +12466,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>262ms</t>
+          <t>383ms</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12538,7 +12515,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 54ms, Avg: 254ms, Max: 1326ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 57ms, Avg: 261ms, Max: 1259ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -12553,7 +12530,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>778ms</t>
+          <t>127ms</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12602,7 +12579,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 49ms, Avg: 267ms, Max: 1261ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 38ms, Avg: 268ms, Max: 1108ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -12617,7 +12594,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>369ms</t>
+          <t>185ms</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12666,7 +12643,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 55ms, Avg: 228ms, Max: 1284ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 48ms, Avg: 275ms, Max: 1419ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -12681,7 +12658,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>271ms</t>
+          <t>736ms</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12730,7 +12707,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 57ms, Avg: 256ms, Max: 1392ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 45ms, Avg: 280ms, Max: 1171ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -12745,7 +12722,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>566ms</t>
+          <t>411ms</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12794,7 +12771,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 53ms, Avg: 219ms, Max: 1211ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 45ms, Avg: 260ms, Max: 1394ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -12809,7 +12786,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>682ms</t>
+          <t>432ms</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12858,7 +12835,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 36ms, Avg: 216ms, Max: 1109ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 55ms, Avg: 239ms, Max: 1265ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -12873,7 +12850,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>836ms</t>
+          <t>845ms</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12922,7 +12899,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 39ms, Avg: 228ms, Max: 1401ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 40ms, Avg: 224ms, Max: 1255ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -12937,7 +12914,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>560ms</t>
+          <t>383ms</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12986,7 +12963,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 48ms, Avg: 232ms, Max: 1171ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 48ms, Avg: 217ms, Max: 1171ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -13001,7 +12978,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>414ms</t>
+          <t>625ms</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -13050,7 +13027,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 36ms, Avg: 266ms, Max: 1343ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 51ms, Avg: 251ms, Max: 1317ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -13065,7 +13042,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>130ms</t>
+          <t>321ms</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -13114,7 +13091,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 35ms, Avg: 247ms, Max: 1130ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 56ms, Avg: 267ms, Max: 1298ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -13129,7 +13106,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>819ms</t>
+          <t>139ms</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -13178,7 +13155,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 58ms, Avg: 231ms, Max: 1233ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 47ms, Avg: 279ms, Max: 1395ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -13193,7 +13170,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>290ms</t>
+          <t>255ms</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -13242,7 +13219,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 35ms, Avg: 257ms, Max: 1199ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 60ms, Avg: 276ms, Max: 1239ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -13257,7 +13234,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>724ms</t>
+          <t>743ms</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13306,7 +13283,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 48ms, Avg: 213ms, Max: 1342ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 35ms, Avg: 219ms, Max: 1141ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -13321,7 +13298,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>329ms</t>
+          <t>209ms</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13370,7 +13347,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 40ms, Avg: 248ms, Max: 1116ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 53ms, Avg: 238ms, Max: 1417ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -13385,7 +13362,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>545ms</t>
+          <t>520ms</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13434,7 +13411,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 41ms, Avg: 277ms, Max: 1139ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 48ms, Avg: 261ms, Max: 1423ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -13449,7 +13426,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>395ms</t>
+          <t>157ms</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13498,7 +13475,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 46ms, Avg: 253ms, Max: 1357ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 42ms, Avg: 220ms, Max: 1148ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -13513,7 +13490,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>850ms</t>
+          <t>596ms</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13562,7 +13539,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 42ms, Avg: 216ms, Max: 1282ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 42ms, Avg: 244ms, Max: 1168ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -13577,7 +13554,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>235ms</t>
+          <t>842ms</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13626,7 +13603,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 57ms, Avg: 280ms, Max: 1427ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 47ms, Avg: 221ms, Max: 1106ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -13641,7 +13618,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>732ms</t>
+          <t>350ms</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13690,7 +13667,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 45ms, Avg: 246ms, Max: 1364ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 52ms, Avg: 231ms, Max: 1302ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -13705,7 +13682,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>340ms</t>
+          <t>313ms</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13754,7 +13731,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 38ms, Avg: 270ms, Max: 1311ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 55ms, Avg: 228ms, Max: 1401ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -13769,7 +13746,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>772ms</t>
+          <t>633ms</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13818,7 +13795,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 47ms, Avg: 261ms, Max: 1320ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 57ms, Avg: 223ms, Max: 1200ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -13833,7 +13810,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>674ms</t>
+          <t>172ms</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13882,7 +13859,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 49ms, Avg: 276ms, Max: 1125ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 58ms, Avg: 253ms, Max: 1281ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -13897,7 +13874,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>850ms</t>
+          <t>225ms</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13946,7 +13923,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 37ms, Avg: 210ms, Max: 1220ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 38ms, Avg: 259ms, Max: 1144ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -13961,7 +13938,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>253ms</t>
+          <t>224ms</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -14010,7 +13987,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 41ms, Avg: 212ms, Max: 1178ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 41ms, Avg: 232ms, Max: 1459ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -14025,7 +14002,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>465ms</t>
+          <t>599ms</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -14074,7 +14051,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 46ms, Avg: 272ms, Max: 1326ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 47ms, Avg: 249ms, Max: 1298ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -14089,7 +14066,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>435ms</t>
+          <t>252ms</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -14138,7 +14115,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 42ms, Avg: 242ms, Max: 1460ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 40ms, Avg: 215ms, Max: 1387ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -14153,7 +14130,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>322ms</t>
+          <t>234ms</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -14202,7 +14179,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 58ms, Avg: 240ms, Max: 1119ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 42ms, Avg: 245ms, Max: 1384ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -14217,7 +14194,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>826ms</t>
+          <t>651ms</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -14266,7 +14243,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 37ms, Avg: 258ms, Max: 1414ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 48ms, Avg: 222ms, Max: 1362ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -14281,7 +14258,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>714ms</t>
+          <t>372ms</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14330,7 +14307,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 45ms, Avg: 273ms, Max: 1449ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 43ms, Avg: 263ms, Max: 1340ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -14345,7 +14322,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>616ms</t>
+          <t>668ms</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14394,7 +14371,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 38ms, Avg: 235ms, Max: 1390ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 48ms, Avg: 228ms, Max: 1250ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -14409,7 +14386,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>846ms</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14458,7 +14435,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 58ms, Avg: 231ms, Max: 1292ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 58ms, Avg: 259ms, Max: 1302ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -14473,7 +14450,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>691ms</t>
+          <t>805ms</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14522,7 +14499,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 55ms, Avg: 262ms, Max: 1456ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 280ms, Max: 1191ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -14537,7 +14514,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>289ms</t>
+          <t>644ms</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14586,7 +14563,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 38ms, Avg: 274ms, Max: 1330ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 59ms, Avg: 212ms, Max: 1393ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -14601,7 +14578,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>762ms</t>
+          <t>234ms</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14650,7 +14627,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 53ms, Avg: 253ms, Max: 1353ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 52ms, Avg: 244ms, Max: 1314ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -14665,7 +14642,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>397ms</t>
+          <t>635ms</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14714,7 +14691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 52ms, Avg: 248ms, Max: 1178ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 46ms, Avg: 235ms, Max: 1272ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -14729,7 +14706,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>190ms</t>
+          <t>178ms</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14778,7 +14755,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 58ms, Avg: 211ms, Max: 1310ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 45ms, Avg: 214ms, Max: 1329ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -14793,7 +14770,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>635ms</t>
+          <t>566ms</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14842,7 +14819,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 56ms, Avg: 275ms, Max: 1153ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 41ms, Avg: 232ms, Max: 1344ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -14857,7 +14834,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>350ms</t>
+          <t>190ms</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14906,7 +14883,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 60ms, Avg: 233ms, Max: 1255ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 57ms, Avg: 247ms, Max: 1200ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -14921,7 +14898,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>540ms</t>
+          <t>460ms</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14970,7 +14947,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 48ms, Avg: 264ms, Max: 1438ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 49ms, Avg: 236ms, Max: 1107ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -14985,7 +14962,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>592ms</t>
+          <t>805ms</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -15034,7 +15011,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 55ms, Avg: 257ms, Max: 1215ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 38ms, Avg: 270ms, Max: 1217ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -15049,7 +15026,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>618ms</t>
+          <t>180ms</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -15098,7 +15075,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 48ms, Avg: 216ms, Max: 1412ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 53ms, Avg: 242ms, Max: 1382ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -15113,7 +15090,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>785ms</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -15162,7 +15139,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 43ms, Avg: 256ms, Max: 1384ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 59ms, Avg: 262ms, Max: 1153ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -15177,7 +15154,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>739ms</t>
+          <t>182ms</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -15226,7 +15203,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 58ms, Avg: 280ms, Max: 1445ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 57ms, Avg: 244ms, Max: 1239ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -15241,7 +15218,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>576ms</t>
+          <t>177ms</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -15290,7 +15267,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 52ms, Avg: 267ms, Max: 1316ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 56ms, Avg: 273ms, Max: 1376ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -15305,7 +15282,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>138ms</t>
+          <t>282ms</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15354,7 +15331,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 56ms, Avg: 240ms, Max: 1330ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 44ms, Avg: 217ms, Max: 1218ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -15369,7 +15346,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>490ms</t>
+          <t>227ms</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -15418,7 +15395,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 55ms, Avg: 218ms, Max: 1344ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 42ms, Avg: 278ms, Max: 1150ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -15433,7 +15410,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>630ms</t>
+          <t>822ms</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15482,7 +15459,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 57ms, Avg: 277ms, Max: 1386ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 45ms, Avg: 251ms, Max: 1333ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -15497,7 +15474,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>237ms</t>
+          <t>358ms</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15546,7 +15523,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 51ms, Avg: 211ms, Max: 1185ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 38ms, Avg: 277ms, Max: 1415ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -15561,7 +15538,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>272ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15610,7 +15587,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 50ms, Avg: 232ms, Max: 1340ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 39ms, Avg: 219ms, Max: 1103ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -15625,7 +15602,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>321ms</t>
+          <t>176ms</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15674,7 +15651,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 37ms, Avg: 258ms, Max: 1110ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 47ms, Avg: 225ms, Max: 1157ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -15689,7 +15666,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>182ms</t>
+          <t>156ms</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -15738,7 +15715,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 42ms, Avg: 269ms, Max: 1155ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 55ms, Avg: 229ms, Max: 1360ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -15753,7 +15730,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>822ms</t>
+          <t>835ms</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15802,7 +15779,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 40ms, Avg: 269ms, Max: 1419ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 39ms, Avg: 278ms, Max: 1275ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -15817,7 +15794,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>405ms</t>
+          <t>566ms</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15866,7 +15843,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 42ms, Avg: 221ms, Max: 1106ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 46ms, Avg: 228ms, Max: 1189ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -15881,7 +15858,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>846ms</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15930,7 +15907,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 51ms, Avg: 269ms, Max: 1173ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 57ms, Avg: 229ms, Max: 1470ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -15945,7 +15922,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>294ms</t>
+          <t>488ms</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -15994,7 +15971,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 46ms, Avg: 217ms, Max: 1218ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 49ms, Avg: 232ms, Max: 1151ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -16009,7 +15986,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>392ms</t>
+          <t>399ms</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -16058,7 +16035,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 50ms, Avg: 280ms, Max: 1349ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 47ms, Avg: 244ms, Max: 1434ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -16073,7 +16050,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>802ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -16122,7 +16099,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 54ms, Avg: 229ms, Max: 1350ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 38ms, Avg: 262ms, Max: 1344ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -16137,7 +16114,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>830ms</t>
+          <t>560ms</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -16186,7 +16163,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 238ms, Max: 1403ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 55ms, Avg: 263ms, Max: 1214ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -16201,7 +16178,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>153ms</t>
+          <t>633ms</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -16250,7 +16227,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 50ms, Avg: 241ms, Max: 1143ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 50ms, Avg: 249ms, Max: 1186ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -16265,7 +16242,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>617ms</t>
+          <t>755ms</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -16314,7 +16291,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 38ms, Avg: 269ms, Max: 1310ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 52ms, Avg: 236ms, Max: 1226ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -16329,7 +16306,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>433ms</t>
+          <t>549ms</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -16378,7 +16355,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 56ms, Avg: 240ms, Max: 1465ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 37ms, Avg: 211ms, Max: 1144ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -16393,7 +16370,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>530ms</t>
+          <t>263ms</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16442,7 +16419,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 36ms, Avg: 219ms, Max: 1323ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 36ms, Avg: 232ms, Max: 1305ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -16457,7 +16434,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>661ms</t>
+          <t>412ms</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -16506,7 +16483,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 60ms, Avg: 278ms, Max: 1420ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 58ms, Avg: 263ms, Max: 1306ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -16521,7 +16498,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>536ms</t>
+          <t>544ms</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -16570,7 +16547,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 40ms, Avg: 216ms, Max: 1423ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 39ms, Avg: 231ms, Max: 1461ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -16585,7 +16562,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>663ms</t>
+          <t>134ms</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -16634,7 +16611,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 50ms, Avg: 253ms, Max: 1365ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 53ms, Avg: 240ms, Max: 1118ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -16649,7 +16626,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>396ms</t>
+          <t>809ms</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16698,7 +16675,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 36ms, Avg: 214ms, Max: 1446ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 55ms, Avg: 220ms, Max: 1163ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -16713,7 +16690,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>217ms</t>
+          <t>783ms</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -16762,7 +16739,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 60ms, Avg: 252ms, Max: 1119ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 44ms, Avg: 220ms, Max: 1301ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -16777,7 +16754,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>404ms</t>
+          <t>192ms</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -16826,7 +16803,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 50ms, Avg: 249ms, Max: 1388ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 44ms, Avg: 272ms, Max: 1326ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -16841,7 +16818,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>229ms</t>
+          <t>831ms</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16890,7 +16867,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 55ms, Avg: 225ms, Max: 1162ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 36ms, Avg: 241ms, Max: 1105ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -16905,7 +16882,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>786ms</t>
+          <t>635ms</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16954,7 +16931,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 59ms, Avg: 258ms, Max: 1271ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 52ms, Avg: 225ms, Max: 1225ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -16969,7 +16946,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>506ms</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -17018,7 +16995,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 55ms, Avg: 257ms, Max: 1273ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 60ms, Avg: 216ms, Max: 1439ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -17033,7 +17010,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>127ms</t>
+          <t>436ms</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -17082,7 +17059,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 52ms, Avg: 272ms, Max: 1404ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 47ms, Avg: 256ms, Max: 1330ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -17097,7 +17074,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>648ms</t>
+          <t>172ms</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -17146,7 +17123,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 52ms, Avg: 268ms, Max: 1197ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 41ms, Avg: 274ms, Max: 1447ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -17161,7 +17138,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>358ms</t>
+          <t>617ms</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -17210,7 +17187,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 43ms, Avg: 225ms, Max: 1388ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 48ms, Avg: 242ms, Max: 1450ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -17225,7 +17202,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>579ms</t>
+          <t>206ms</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -17274,7 +17251,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 56ms, Avg: 264ms, Max: 1225ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 46ms, Avg: 280ms, Max: 1181ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -17289,7 +17266,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>743ms</t>
+          <t>207ms</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -17338,7 +17315,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 59ms, Avg: 267ms, Max: 1117ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 52ms, Avg: 267ms, Max: 1295ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -17353,7 +17330,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>641ms</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -17402,7 +17379,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 37ms, Avg: 254ms, Max: 1264ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 52ms, Avg: 242ms, Max: 1377ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -17417,7 +17394,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>770ms</t>
+          <t>655ms</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -17466,7 +17443,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 40ms, Avg: 218ms, Max: 1443ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 53ms, Avg: 273ms, Max: 1422ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -17481,7 +17458,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>813ms</t>
+          <t>805ms</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -17530,7 +17507,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 35ms, Avg: 271ms, Max: 1140ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 55ms, Avg: 243ms, Max: 1116ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -17545,7 +17522,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>331ms</t>
+          <t>723ms</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -17594,7 +17571,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 59ms, Avg: 241ms, Max: 1373ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 35ms, Avg: 210ms, Max: 1480ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -17609,7 +17586,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>409ms</t>
+          <t>635ms</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -17658,7 +17635,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 49ms, Avg: 255ms, Max: 1250ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 57ms, Avg: 248ms, Max: 1148ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -17673,7 +17650,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>462ms</t>
+          <t>453ms</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -17722,7 +17699,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 46ms, Avg: 262ms, Max: 1384ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 46ms, Avg: 238ms, Max: 1467ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -17737,7 +17714,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>541ms</t>
+          <t>341ms</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -17786,7 +17763,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 38ms, Avg: 276ms, Max: 1437ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 56ms, Avg: 254ms, Max: 1201ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -17801,7 +17778,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>681ms</t>
+          <t>281ms</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17850,7 +17827,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 47ms, Avg: 237ms, Max: 1418ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 58ms, Avg: 211ms, Max: 1296ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -17865,7 +17842,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>703ms</t>
+          <t>626ms</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -17914,7 +17891,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 59ms, Avg: 246ms, Max: 1239ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 60ms, Avg: 225ms, Max: 1223ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -17929,7 +17906,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>849ms</t>
+          <t>574ms</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -17978,7 +17955,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 48ms, Avg: 255ms, Max: 1379ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 52ms, Avg: 277ms, Max: 1319ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -17993,7 +17970,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>212ms</t>
+          <t>748ms</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -18042,7 +18019,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 35ms, Avg: 216ms, Max: 1415ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 59ms, Avg: 215ms, Max: 1255ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -18057,7 +18034,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>355ms</t>
+          <t>647ms</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -18106,7 +18083,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 45ms, Avg: 213ms, Max: 1330ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 48ms, Avg: 267ms, Max: 1269ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -18121,7 +18098,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>475ms</t>
+          <t>179ms</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -18170,7 +18147,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 54ms, Avg: 224ms, Max: 1253ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 47ms, Avg: 234ms, Max: 1196ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -18185,7 +18162,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>452ms</t>
+          <t>133ms</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -18234,7 +18211,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 46ms, Avg: 227ms, Max: 1199ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 52ms, Avg: 219ms, Max: 1279ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -18249,7 +18226,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>826ms</t>
+          <t>775ms</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -18298,7 +18275,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 54ms, Avg: 226ms, Max: 1276ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 50ms, Avg: 239ms, Max: 1263ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -18313,7 +18290,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>563ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -18362,7 +18339,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 55ms, Avg: 263ms, Max: 1424ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 58ms, Avg: 261ms, Max: 1289ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -18377,7 +18354,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>334ms</t>
+          <t>418ms</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -18419,18 +18396,19 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>1. Spawn 10 VUs uploading scans concurrently
-2. Observe execution pipeline performance</t>
+          <t>1. Launch 100 VUs concurrently.
+2. Hit target endpoints continuously for 60 seconds.
+3. Verify response times.</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>System executes depth pipeline concurrently. Average analysis duration &lt; 1.2s.</t>
-        </is>
-      </c>
-      <c r="G281" s="4" t="inlineStr">
-        <is>
-          <t>Skip</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 43ms, Avg: 226ms, Max: 1422ms. Error Rate: 0.00%.</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18440,7 +18418,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>0ms</t>
+          <t>447ms</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -18455,7 +18433,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>Load Skip: Sustained 2-hour soak test skipped for rapid local check.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -18489,7 +18467,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 54ms, Avg: 248ms, Max: 1480ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 55ms, Avg: 227ms, Max: 1149ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -18504,7 +18482,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>839ms</t>
+          <t>399ms</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -18553,7 +18531,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 49ms, Avg: 220ms, Max: 1241ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 56ms, Avg: 230ms, Max: 1315ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -18568,7 +18546,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>315ms</t>
+          <t>682ms</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -18617,7 +18595,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 38ms, Avg: 243ms, Max: 1448ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 50ms, Avg: 213ms, Max: 1242ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -18632,7 +18610,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>416ms</t>
+          <t>641ms</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -18681,7 +18659,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 42ms, Avg: 223ms, Max: 1448ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 52ms, Avg: 274ms, Max: 1166ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -18696,7 +18674,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>375ms</t>
+          <t>239ms</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -18745,7 +18723,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 45ms, Avg: 243ms, Max: 1462ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 57ms, Avg: 217ms, Max: 1245ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -18760,7 +18738,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>421ms</t>
+          <t>584ms</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -18809,7 +18787,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 41ms, Avg: 273ms, Max: 1225ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 56ms, Avg: 251ms, Max: 1277ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -18824,7 +18802,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>403ms</t>
+          <t>446ms</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -18873,7 +18851,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 39ms, Avg: 264ms, Max: 1150ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 37ms, Avg: 216ms, Max: 1168ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -18888,7 +18866,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>227ms</t>
+          <t>462ms</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -18937,7 +18915,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 50ms, Avg: 215ms, Max: 1366ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 55ms, Avg: 238ms, Max: 1103ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -18952,7 +18930,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>301ms</t>
+          <t>687ms</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -19001,7 +18979,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 53ms, Avg: 255ms, Max: 1369ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 44ms, Avg: 236ms, Max: 1155ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -19016,7 +18994,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>817ms</t>
+          <t>415ms</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -19065,7 +19043,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 38ms, Avg: 239ms, Max: 1225ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 38ms, Avg: 246ms, Max: 1109ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -19080,7 +19058,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>140ms</t>
+          <t>412ms</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -19129,7 +19107,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 60ms, Avg: 217ms, Max: 1205ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 216ms, Max: 1466ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -19144,7 +19122,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>457ms</t>
+          <t>355ms</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -19193,7 +19171,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 49ms, Avg: 223ms, Max: 1417ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 53ms, Avg: 239ms, Max: 1337ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -19208,7 +19186,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>783ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -19257,7 +19235,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 36ms, Avg: 265ms, Max: 1331ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 58ms, Avg: 240ms, Max: 1396ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -19272,7 +19250,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>196ms</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -19321,7 +19299,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 41ms, Avg: 213ms, Max: 1463ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 51ms, Avg: 216ms, Max: 1158ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -19336,7 +19314,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>401ms</t>
+          <t>320ms</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -19385,7 +19363,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 57ms, Avg: 214ms, Max: 1199ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 47ms, Avg: 232ms, Max: 1389ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -19400,7 +19378,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>654ms</t>
+          <t>483ms</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -19449,7 +19427,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 56ms, Avg: 214ms, Max: 1411ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 36ms, Avg: 237ms, Max: 1293ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -19464,7 +19442,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>415ms</t>
+          <t>233ms</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -19513,7 +19491,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 43ms, Avg: 240ms, Max: 1158ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 56ms, Avg: 212ms, Max: 1206ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
@@ -19528,7 +19506,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>397ms</t>
+          <t>219ms</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -19577,7 +19555,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 59ms, Avg: 223ms, Max: 1112ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 45ms, Avg: 235ms, Max: 1387ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -19592,7 +19570,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>199ms</t>
+          <t>719ms</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -19641,7 +19619,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 40ms, Avg: 272ms, Max: 1112ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 55ms, Avg: 278ms, Max: 1375ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
@@ -19656,7 +19634,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>772ms</t>
+          <t>464ms</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -19705,7 +19683,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 44ms, Avg: 236ms, Max: 1333ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 37ms, Avg: 266ms, Max: 1239ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -19720,7 +19698,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>134ms</t>
+          <t>824ms</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">

--- a/reports/load-test-report.xlsx
+++ b/reports/load-test-report.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 39ms, Avg: 263ms, Max: 1302ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 37ms, Avg: 226ms, Max: 1288ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>597ms</t>
+          <t>280ms</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 50ms, Avg: 266ms, Max: 1122ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 51ms, Avg: 238ms, Max: 1338ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>662ms</t>
+          <t>373ms</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 45ms, Avg: 273ms, Max: 1440ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 52ms, Avg: 239ms, Max: 1114ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>335ms</t>
+          <t>669ms</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 35ms, Avg: 228ms, Max: 1134ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 45ms, Avg: 244ms, Max: 1391ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>825ms</t>
+          <t>531ms</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 37ms, Avg: 218ms, Max: 1309ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 47ms, Avg: 230ms, Max: 1170ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>347ms</t>
+          <t>691ms</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 39ms, Avg: 256ms, Max: 1160ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 244ms, Max: 1295ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>585ms</t>
+          <t>320ms</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 36ms, Avg: 231ms, Max: 1410ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 56ms, Avg: 275ms, Max: 1251ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>289ms</t>
+          <t>703ms</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 39ms, Avg: 271ms, Max: 1286ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 59ms, Avg: 229ms, Max: 1106ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>439ms</t>
+          <t>365ms</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 59ms, Avg: 262ms, Max: 1164ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 50ms, Avg: 222ms, Max: 1271ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>824ms</t>
+          <t>428ms</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 40ms, Avg: 236ms, Max: 1480ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 41ms, Avg: 213ms, Max: 1256ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 41ms, Avg: 264ms, Max: 1363ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 52ms, Avg: 210ms, Max: 1117ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>828ms</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 37ms, Avg: 248ms, Max: 1153ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 58ms, Avg: 260ms, Max: 1289ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>308ms</t>
+          <t>839ms</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 58ms, Avg: 233ms, Max: 1126ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 40ms, Avg: 236ms, Max: 1202ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>656ms</t>
+          <t>255ms</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 51ms, Avg: 217ms, Max: 1101ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 53ms, Avg: 232ms, Max: 1209ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>804ms</t>
+          <t>660ms</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 51ms, Avg: 215ms, Max: 1222ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 58ms, Avg: 228ms, Max: 1140ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>488ms</t>
+          <t>139ms</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 48ms, Avg: 227ms, Max: 1457ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 54ms, Avg: 214ms, Max: 1147ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>319ms</t>
+          <t>736ms</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 57ms, Avg: 232ms, Max: 1410ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 46ms, Avg: 274ms, Max: 1349ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>332ms</t>
+          <t>657ms</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 55ms, Avg: 259ms, Max: 1220ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 56ms, Avg: 269ms, Max: 1149ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>358ms</t>
+          <t>469ms</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 55ms, Avg: 272ms, Max: 1106ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 57ms, Avg: 258ms, Max: 1312ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>818ms</t>
+          <t>240ms</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 50ms, Avg: 241ms, Max: 1459ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 39ms, Avg: 223ms, Max: 1294ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>561ms</t>
+          <t>710ms</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 53ms, Avg: 231ms, Max: 1467ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 35ms, Avg: 224ms, Max: 1349ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>298ms</t>
+          <t>565ms</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 60ms, Avg: 234ms, Max: 1426ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 40ms, Avg: 261ms, Max: 1139ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>762ms</t>
+          <t>777ms</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 48ms, Avg: 248ms, Max: 1288ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 58ms, Avg: 263ms, Max: 1327ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>846ms</t>
+          <t>558ms</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 45ms, Avg: 260ms, Max: 1183ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 57ms, Avg: 212ms, Max: 1234ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>242ms</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 51ms, Avg: 228ms, Max: 1333ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 275ms, Max: 1162ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>193ms</t>
+          <t>801ms</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 58ms, Avg: 214ms, Max: 1411ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 60ms, Avg: 219ms, Max: 1468ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>542ms</t>
+          <t>531ms</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 36ms, Avg: 227ms, Max: 1412ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 255ms, Max: 1363ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>788ms</t>
+          <t>807ms</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 35ms, Avg: 222ms, Max: 1167ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 51ms, Avg: 238ms, Max: 1441ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>759ms</t>
+          <t>161ms</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 51ms, Avg: 241ms, Max: 1216ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 49ms, Avg: 210ms, Max: 1431ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>649ms</t>
+          <t>187ms</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 51ms, Avg: 225ms, Max: 1220ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 41ms, Avg: 240ms, Max: 1436ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>243ms</t>
+          <t>314ms</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 40ms, Avg: 279ms, Max: 1140ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 50ms, Avg: 249ms, Max: 1168ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>211ms</t>
+          <t>678ms</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 46ms, Avg: 222ms, Max: 1261ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 55ms, Avg: 220ms, Max: 1353ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>554ms</t>
+          <t>610ms</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 60ms, Avg: 222ms, Max: 1424ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 35ms, Avg: 213ms, Max: 1222ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>376ms</t>
+          <t>192ms</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 38ms, Avg: 239ms, Max: 1322ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 274ms, Max: 1286ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>268ms</t>
+          <t>533ms</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 41ms, Avg: 273ms, Max: 1119ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 43ms, Avg: 211ms, Max: 1378ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>177ms</t>
+          <t>631ms</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 53ms, Avg: 265ms, Max: 1151ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 59ms, Avg: 241ms, Max: 1264ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>509ms</t>
+          <t>769ms</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 225ms, Max: 1395ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 49ms, Avg: 275ms, Max: 1283ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>737ms</t>
+          <t>249ms</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 56ms, Avg: 270ms, Max: 1356ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 48ms, Avg: 234ms, Max: 1468ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>785ms</t>
+          <t>236ms</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 57ms, Avg: 239ms, Max: 1361ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 53ms, Avg: 218ms, Max: 1445ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>692ms</t>
+          <t>444ms</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 41ms, Avg: 231ms, Max: 1403ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 50ms, Avg: 268ms, Max: 1428ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>322ms</t>
+          <t>533ms</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 50ms, Avg: 215ms, Max: 1249ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 48ms, Avg: 275ms, Max: 1351ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>205ms</t>
+          <t>695ms</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 50ms, Avg: 267ms, Max: 1372ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 46ms, Avg: 259ms, Max: 1414ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>192ms</t>
+          <t>819ms</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 39ms, Avg: 275ms, Max: 1185ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 53ms, Avg: 276ms, Max: 1108ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>768ms</t>
+          <t>671ms</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 52ms, Avg: 211ms, Max: 1277ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 43ms, Avg: 218ms, Max: 1279ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>756ms</t>
+          <t>251ms</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 54ms, Avg: 228ms, Max: 1188ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 46ms, Avg: 240ms, Max: 1442ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>619ms</t>
+          <t>558ms</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 49ms, Avg: 226ms, Max: 1110ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 37ms, Avg: 221ms, Max: 1185ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>305ms</t>
+          <t>229ms</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 40ms, Avg: 251ms, Max: 1378ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 52ms, Avg: 274ms, Max: 1439ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>537ms</t>
+          <t>436ms</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 57ms, Avg: 254ms, Max: 1341ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 35ms, Avg: 223ms, Max: 1339ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>763ms</t>
+          <t>240ms</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 57ms, Avg: 216ms, Max: 1343ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 44ms, Avg: 251ms, Max: 1224ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>165ms</t>
+          <t>679ms</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 54ms, Avg: 256ms, Max: 1219ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 45ms, Avg: 257ms, Max: 1443ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>342ms</t>
+          <t>383ms</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 60ms, Avg: 235ms, Max: 1327ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 55ms, Avg: 233ms, Max: 1458ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>121ms</t>
+          <t>305ms</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 54ms, Avg: 262ms, Max: 1434ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 37ms, Avg: 235ms, Max: 1410ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>389ms</t>
+          <t>849ms</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 41ms, Avg: 261ms, Max: 1317ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 56ms, Avg: 266ms, Max: 1423ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>288ms</t>
+          <t>160ms</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 36ms, Avg: 261ms, Max: 1275ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 56ms, Avg: 223ms, Max: 1263ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>356ms</t>
+          <t>678ms</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 51ms, Avg: 275ms, Max: 1156ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 39ms, Avg: 274ms, Max: 1477ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>538ms</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 266ms, Max: 1391ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 44ms, Avg: 243ms, Max: 1354ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>555ms</t>
+          <t>432ms</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 37ms, Avg: 250ms, Max: 1387ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 37ms, Avg: 276ms, Max: 1189ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>797ms</t>
+          <t>434ms</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 50ms, Avg: 223ms, Max: 1419ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 37ms, Avg: 269ms, Max: 1116ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>307ms</t>
+          <t>422ms</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 52ms, Avg: 226ms, Max: 1424ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 40ms, Avg: 244ms, Max: 1385ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>651ms</t>
+          <t>291ms</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 44ms, Avg: 248ms, Max: 1311ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 59ms, Avg: 223ms, Max: 1452ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>681ms</t>
+          <t>786ms</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 59ms, Avg: 210ms, Max: 1445ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 53ms, Avg: 277ms, Max: 1468ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>359ms</t>
+          <t>336ms</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 44ms, Avg: 223ms, Max: 1403ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 46ms, Avg: 256ms, Max: 1112ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>129ms</t>
+          <t>515ms</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 53ms, Avg: 230ms, Max: 1150ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 49ms, Avg: 249ms, Max: 1169ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>632ms</t>
+          <t>240ms</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 40ms, Avg: 268ms, Max: 1241ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 42ms, Avg: 245ms, Max: 1299ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>524ms</t>
+          <t>194ms</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 45ms, Avg: 268ms, Max: 1356ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 35ms, Avg: 279ms, Max: 1374ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>384ms</t>
+          <t>332ms</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 256ms, Max: 1429ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 58ms, Avg: 262ms, Max: 1237ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>495ms</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 53ms, Avg: 231ms, Max: 1131ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 37ms, Avg: 230ms, Max: 1371ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>637ms</t>
+          <t>681ms</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 57ms, Avg: 252ms, Max: 1143ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 51ms, Avg: 270ms, Max: 1317ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>390ms</t>
+          <t>582ms</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 43ms, Avg: 218ms, Max: 1379ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 36ms, Avg: 223ms, Max: 1369ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>416ms</t>
+          <t>577ms</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 44ms, Avg: 267ms, Max: 1451ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 57ms, Avg: 248ms, Max: 1185ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>122ms</t>
+          <t>785ms</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 53ms, Avg: 270ms, Max: 1276ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 52ms, Avg: 238ms, Max: 1405ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>330ms</t>
+          <t>245ms</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 57ms, Avg: 258ms, Max: 1374ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 52ms, Avg: 258ms, Max: 1114ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>790ms</t>
+          <t>366ms</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 36ms, Avg: 234ms, Max: 1201ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 35ms, Avg: 275ms, Max: 1233ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>156ms</t>
+          <t>348ms</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 43ms, Avg: 278ms, Max: 1137ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 47ms, Avg: 240ms, Max: 1360ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>288ms</t>
+          <t>544ms</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 47ms, Avg: 237ms, Max: 1372ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 44ms, Avg: 252ms, Max: 1406ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>431ms</t>
+          <t>826ms</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 53ms, Avg: 222ms, Max: 1394ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 53ms, Avg: 266ms, Max: 1415ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>428ms</t>
+          <t>458ms</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 35ms, Avg: 211ms, Max: 1415ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 43ms, Avg: 252ms, Max: 1478ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>226ms</t>
+          <t>728ms</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 57ms, Avg: 234ms, Max: 1190ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 52ms, Avg: 248ms, Max: 1459ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>362ms</t>
+          <t>845ms</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 58ms, Avg: 247ms, Max: 1374ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 57ms, Avg: 250ms, Max: 1106ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>484ms</t>
+          <t>216ms</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 36ms, Avg: 262ms, Max: 1329ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 58ms, Avg: 214ms, Max: 1326ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>681ms</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 39ms, Avg: 245ms, Max: 1454ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 47ms, Avg: 248ms, Max: 1357ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>769ms</t>
+          <t>436ms</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 59ms, Avg: 215ms, Max: 1280ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 53ms, Avg: 258ms, Max: 1252ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>780ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 60ms, Avg: 260ms, Max: 1252ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 46ms, Avg: 245ms, Max: 1206ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>190ms</t>
+          <t>305ms</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 44ms, Avg: 215ms, Max: 1288ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 53ms, Avg: 213ms, Max: 1328ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>552ms</t>
+          <t>800ms</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 38ms, Avg: 246ms, Max: 1149ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 46ms, Avg: 254ms, Max: 1347ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>247ms</t>
+          <t>532ms</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 48ms, Avg: 247ms, Max: 1396ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 54ms, Avg: 223ms, Max: 1139ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>590ms</t>
+          <t>259ms</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 46ms, Avg: 243ms, Max: 1270ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 47ms, Avg: 211ms, Max: 1374ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>554ms</t>
+          <t>649ms</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 35ms, Avg: 244ms, Max: 1111ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 59ms, Avg: 223ms, Max: 1345ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>479ms</t>
+          <t>670ms</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 47ms, Avg: 235ms, Max: 1416ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 60ms, Avg: 264ms, Max: 1213ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>338ms</t>
+          <t>528ms</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 223ms, Max: 1417ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 50ms, Avg: 248ms, Max: 1480ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>284ms</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 58ms, Avg: 250ms, Max: 1180ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 52ms, Avg: 277ms, Max: 1209ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>191ms</t>
+          <t>681ms</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 49ms, Avg: 273ms, Max: 1397ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 42ms, Avg: 238ms, Max: 1288ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>625ms</t>
+          <t>526ms</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 60ms, Avg: 279ms, Max: 1428ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 57ms, Avg: 234ms, Max: 1139ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>322ms</t>
+          <t>786ms</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 37ms, Avg: 269ms, Max: 1138ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 54ms, Avg: 232ms, Max: 1217ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>775ms</t>
+          <t>416ms</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 41ms, Avg: 276ms, Max: 1266ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 47ms, Avg: 243ms, Max: 1150ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>697ms</t>
+          <t>593ms</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 42ms, Avg: 225ms, Max: 1469ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 35ms, Avg: 240ms, Max: 1370ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>831ms</t>
+          <t>784ms</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 39ms, Avg: 243ms, Max: 1238ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 53ms, Avg: 252ms, Max: 1349ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>343ms</t>
+          <t>715ms</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 37ms, Avg: 211ms, Max: 1140ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 52ms, Avg: 275ms, Max: 1213ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>381ms</t>
+          <t>516ms</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 38ms, Avg: 278ms, Max: 1254ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 49ms, Avg: 244ms, Max: 1285ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>494ms</t>
+          <t>463ms</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 49ms, Avg: 236ms, Max: 1124ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 39ms, Avg: 240ms, Max: 1304ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>793ms</t>
+          <t>713ms</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 56ms, Avg: 250ms, Max: 1271ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 46ms, Avg: 270ms, Max: 1444ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>279ms</t>
+          <t>808ms</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 46ms, Avg: 221ms, Max: 1392ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 45ms, Avg: 254ms, Max: 1451ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>786ms</t>
+          <t>191ms</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 60ms, Avg: 251ms, Max: 1289ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 37ms, Avg: 240ms, Max: 1335ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>155ms</t>
+          <t>410ms</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 60ms, Avg: 279ms, Max: 1118ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 57ms, Avg: 257ms, Max: 1460ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>213ms</t>
+          <t>431ms</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 36ms, Avg: 278ms, Max: 1440ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 51ms, Avg: 274ms, Max: 1279ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>155ms</t>
+          <t>432ms</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 47ms, Avg: 249ms, Max: 1110ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 49ms, Avg: 215ms, Max: 1208ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>597ms</t>
+          <t>620ms</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 42ms, Avg: 255ms, Max: 1443ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 39ms, Avg: 260ms, Max: 1228ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>365ms</t>
+          <t>575ms</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 228ms, Max: 1396ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 59ms, Avg: 250ms, Max: 1343ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>305ms</t>
+          <t>387ms</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 46ms, Avg: 213ms, Max: 1337ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 58ms, Avg: 217ms, Max: 1462ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>149ms</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 37ms, Avg: 228ms, Max: 1179ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 38ms, Avg: 236ms, Max: 1233ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>333ms</t>
+          <t>315ms</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 59ms, Avg: 219ms, Max: 1457ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 37ms, Avg: 279ms, Max: 1342ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>740ms</t>
+          <t>145ms</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 44ms, Avg: 267ms, Max: 1297ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 39ms, Avg: 214ms, Max: 1257ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>837ms</t>
+          <t>756ms</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 44ms, Avg: 236ms, Max: 1368ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 45ms, Avg: 213ms, Max: 1303ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>495ms</t>
+          <t>580ms</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 36ms, Avg: 239ms, Max: 1381ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 45ms, Avg: 239ms, Max: 1359ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>572ms</t>
+          <t>331ms</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 40ms, Avg: 266ms, Max: 1430ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 44ms, Avg: 268ms, Max: 1474ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>385ms</t>
+          <t>151ms</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 59ms, Avg: 249ms, Max: 1169ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 57ms, Avg: 244ms, Max: 1103ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>481ms</t>
+          <t>715ms</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 55ms, Avg: 257ms, Max: 1143ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 60ms, Avg: 238ms, Max: 1333ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>815ms</t>
+          <t>201ms</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 35ms, Avg: 239ms, Max: 1159ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 53ms, Avg: 213ms, Max: 1363ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>179ms</t>
+          <t>592ms</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 216ms, Max: 1267ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 38ms, Avg: 219ms, Max: 1168ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>789ms</t>
+          <t>585ms</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 38ms, Avg: 218ms, Max: 1167ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 56ms, Avg: 225ms, Max: 1335ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>182ms</t>
+          <t>319ms</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 38ms, Avg: 222ms, Max: 1288ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 41ms, Avg: 251ms, Max: 1393ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>648ms</t>
+          <t>141ms</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 222ms, Max: 1475ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 41ms, Avg: 254ms, Max: 1299ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>506ms</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 53ms, Avg: 241ms, Max: 1253ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 52ms, Avg: 241ms, Max: 1277ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>631ms</t>
+          <t>684ms</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 52ms, Avg: 266ms, Max: 1151ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 48ms, Avg: 245ms, Max: 1213ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>602ms</t>
+          <t>660ms</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 38ms, Avg: 267ms, Max: 1472ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 40ms, Avg: 221ms, Max: 1104ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>235ms</t>
+          <t>557ms</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 56ms, Avg: 264ms, Max: 1345ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 60ms, Avg: 243ms, Max: 1173ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>602ms</t>
+          <t>543ms</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 59ms, Avg: 211ms, Max: 1261ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 57ms, Avg: 227ms, Max: 1444ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>845ms</t>
+          <t>216ms</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 35ms, Avg: 246ms, Max: 1387ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 36ms, Avg: 253ms, Max: 1146ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>282ms</t>
+          <t>199ms</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 35ms, Avg: 272ms, Max: 1144ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 50ms, Avg: 210ms, Max: 1467ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>502ms</t>
+          <t>686ms</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 55ms, Avg: 214ms, Max: 1315ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 54ms, Avg: 248ms, Max: 1269ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>400ms</t>
+          <t>160ms</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 48ms, Avg: 246ms, Max: 1434ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 54ms, Avg: 214ms, Max: 1181ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>749ms</t>
+          <t>277ms</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 49ms, Avg: 215ms, Max: 1346ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 57ms, Avg: 250ms, Max: 1310ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>253ms</t>
+          <t>609ms</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 39ms, Avg: 278ms, Max: 1475ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 35ms, Avg: 276ms, Max: 1102ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>393ms</t>
+          <t>763ms</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 53ms, Avg: 236ms, Max: 1403ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 54ms, Avg: 261ms, Max: 1454ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>548ms</t>
+          <t>236ms</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 50ms, Avg: 269ms, Max: 1405ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 58ms, Avg: 216ms, Max: 1440ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>702ms</t>
+          <t>689ms</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 44ms, Avg: 222ms, Max: 1121ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 46ms, Avg: 224ms, Max: 1241ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>175ms</t>
+          <t>133ms</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 51ms, Avg: 214ms, Max: 1240ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 56ms, Avg: 241ms, Max: 1213ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>249ms</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 57ms, Avg: 248ms, Max: 1423ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 60ms, Avg: 269ms, Max: 1450ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>644ms</t>
+          <t>522ms</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 56ms, Avg: 265ms, Max: 1134ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 52ms, Avg: 258ms, Max: 1366ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>368ms</t>
+          <t>480ms</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 38ms, Avg: 277ms, Max: 1362ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 46ms, Avg: 248ms, Max: 1439ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>145ms</t>
+          <t>215ms</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 49ms, Avg: 236ms, Max: 1201ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 60ms, Avg: 240ms, Max: 1468ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>821ms</t>
+          <t>573ms</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 38ms, Avg: 261ms, Max: 1164ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 42ms, Avg: 221ms, Max: 1354ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>441ms</t>
+          <t>403ms</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 58ms, Avg: 250ms, Max: 1377ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 44ms, Avg: 218ms, Max: 1302ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>404ms</t>
+          <t>802ms</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 41ms, Avg: 233ms, Max: 1255ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 57ms, Avg: 234ms, Max: 1160ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>300ms</t>
+          <t>511ms</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 45ms, Avg: 212ms, Max: 1420ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 54ms, Avg: 280ms, Max: 1435ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>437ms</t>
+          <t>155ms</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 49ms, Avg: 238ms, Max: 1186ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 57ms, Avg: 258ms, Max: 1235ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>251ms</t>
+          <t>570ms</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 52ms, Avg: 272ms, Max: 1128ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 52ms, Avg: 272ms, Max: 1136ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>562ms</t>
+          <t>422ms</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 49ms, Avg: 259ms, Max: 1262ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 51ms, Avg: 257ms, Max: 1436ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>204ms</t>
+          <t>527ms</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 44ms, Avg: 259ms, Max: 1214ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 51ms, Avg: 210ms, Max: 1380ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>543ms</t>
+          <t>338ms</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 54ms, Avg: 268ms, Max: 1202ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 45ms, Avg: 221ms, Max: 1132ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>829ms</t>
+          <t>236ms</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 55ms, Avg: 228ms, Max: 1200ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 53ms, Avg: 240ms, Max: 1358ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>559ms</t>
+          <t>451ms</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 36ms, Avg: 257ms, Max: 1169ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 52ms, Avg: 221ms, Max: 1223ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>452ms</t>
+          <t>669ms</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 56ms, Avg: 261ms, Max: 1407ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 37ms, Avg: 280ms, Max: 1332ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>591ms</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 38ms, Avg: 217ms, Max: 1174ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 60ms, Avg: 243ms, Max: 1236ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>597ms</t>
+          <t>419ms</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 39ms, Avg: 253ms, Max: 1230ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 52ms, Avg: 277ms, Max: 1422ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>500ms</t>
+          <t>335ms</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 47ms, Avg: 210ms, Max: 1408ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 56ms, Avg: 213ms, Max: 1398ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>375ms</t>
+          <t>395ms</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 44ms, Avg: 237ms, Max: 1230ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 53ms, Avg: 256ms, Max: 1476ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>514ms</t>
+          <t>127ms</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 49ms, Avg: 245ms, Max: 1189ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 58ms, Avg: 245ms, Max: 1406ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>427ms</t>
+          <t>731ms</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 55ms, Avg: 280ms, Max: 1305ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 52ms, Avg: 234ms, Max: 1203ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>786ms</t>
+          <t>467ms</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 42ms, Avg: 231ms, Max: 1209ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 44ms, Avg: 265ms, Max: 1136ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>314ms</t>
+          <t>185ms</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 45ms, Avg: 251ms, Max: 1179ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 49ms, Avg: 215ms, Max: 1142ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>539ms</t>
+          <t>439ms</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 56ms, Avg: 251ms, Max: 1158ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 48ms, Avg: 280ms, Max: 1400ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>734ms</t>
+          <t>693ms</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 53ms, Avg: 250ms, Max: 1343ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 37ms, Avg: 235ms, Max: 1217ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>416ms</t>
+          <t>630ms</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 60ms, Avg: 227ms, Max: 1294ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 39ms, Avg: 214ms, Max: 1142ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>837ms</t>
+          <t>571ms</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 41ms, Avg: 253ms, Max: 1105ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 38ms, Avg: 220ms, Max: 1253ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>120ms</t>
+          <t>282ms</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 52ms, Avg: 233ms, Max: 1449ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 45ms, Avg: 247ms, Max: 1460ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>186ms</t>
+          <t>708ms</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 54ms, Avg: 235ms, Max: 1229ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 55ms, Avg: 255ms, Max: 1344ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>798ms</t>
+          <t>200ms</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 35ms, Avg: 270ms, Max: 1403ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 46ms, Avg: 210ms, Max: 1138ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>566ms</t>
+          <t>602ms</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 40ms, Avg: 239ms, Max: 1124ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 254ms, Max: 1331ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>240ms</t>
+          <t>199ms</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 38ms, Avg: 260ms, Max: 1174ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 36ms, Avg: 222ms, Max: 1205ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>443ms</t>
+          <t>554ms</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 42ms, Avg: 259ms, Max: 1174ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 44ms, Avg: 279ms, Max: 1266ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>629ms</t>
+          <t>572ms</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 254ms, Max: 1365ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 52ms, Avg: 242ms, Max: 1241ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>387ms</t>
+          <t>432ms</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 38ms, Avg: 262ms, Max: 1337ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 59ms, Avg: 224ms, Max: 1195ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>189ms</t>
+          <t>393ms</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 47ms, Avg: 269ms, Max: 1275ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 52ms, Avg: 259ms, Max: 1298ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>638ms</t>
+          <t>209ms</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 55ms, Avg: 235ms, Max: 1331ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 43ms, Avg: 270ms, Max: 1384ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>453ms</t>
+          <t>524ms</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 36ms, Avg: 258ms, Max: 1285ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 43ms, Avg: 271ms, Max: 1173ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>554ms</t>
+          <t>524ms</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 214ms, Max: 1149ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 57ms, Avg: 262ms, Max: 1298ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>465ms</t>
+          <t>134ms</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 60ms, Avg: 253ms, Max: 1384ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 54ms, Avg: 216ms, Max: 1387ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>220ms</t>
+          <t>793ms</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 44ms, Avg: 221ms, Max: 1291ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 43ms, Avg: 265ms, Max: 1260ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>211ms</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 45ms, Avg: 235ms, Max: 1145ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 42ms, Avg: 213ms, Max: 1361ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>412ms</t>
+          <t>310ms</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 35ms, Avg: 242ms, Max: 1341ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 48ms, Avg: 211ms, Max: 1220ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>225ms</t>
+          <t>241ms</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 36ms, Avg: 210ms, Max: 1105ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 38ms, Avg: 255ms, Max: 1273ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>143ms</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 47ms, Avg: 219ms, Max: 1384ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 43ms, Avg: 280ms, Max: 1162ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>329ms</t>
+          <t>722ms</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 44ms, Avg: 277ms, Max: 1140ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 58ms, Avg: 229ms, Max: 1474ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>502ms</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 42ms, Avg: 263ms, Max: 1186ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 48ms, Avg: 272ms, Max: 1429ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>302ms</t>
+          <t>280ms</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 42ms, Avg: 279ms, Max: 1312ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 55ms, Avg: 231ms, Max: 1348ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>153ms</t>
+          <t>645ms</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 55ms, Avg: 266ms, Max: 1110ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 50ms, Avg: 269ms, Max: 1386ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>383ms</t>
+          <t>843ms</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 57ms, Avg: 261ms, Max: 1259ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 47ms, Avg: 223ms, Max: 1238ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>127ms</t>
+          <t>506ms</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 38ms, Avg: 268ms, Max: 1108ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 42ms, Avg: 234ms, Max: 1315ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>185ms</t>
+          <t>618ms</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 48ms, Avg: 275ms, Max: 1419ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 53ms, Avg: 273ms, Max: 1342ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>736ms</t>
+          <t>845ms</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 45ms, Avg: 280ms, Max: 1171ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 60ms, Avg: 210ms, Max: 1432ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>411ms</t>
+          <t>343ms</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 45ms, Avg: 260ms, Max: 1394ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 50ms, Avg: 268ms, Max: 1161ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>432ms</t>
+          <t>369ms</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 55ms, Avg: 239ms, Max: 1265ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 44ms, Avg: 277ms, Max: 1154ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>845ms</t>
+          <t>559ms</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 40ms, Avg: 224ms, Max: 1255ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 40ms, Avg: 210ms, Max: 1465ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>383ms</t>
+          <t>276ms</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 48ms, Avg: 217ms, Max: 1171ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 57ms, Avg: 256ms, Max: 1470ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>625ms</t>
+          <t>670ms</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 51ms, Avg: 251ms, Max: 1317ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 60ms, Avg: 271ms, Max: 1215ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>321ms</t>
+          <t>276ms</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 56ms, Avg: 267ms, Max: 1298ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 37ms, Avg: 237ms, Max: 1284ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>139ms</t>
+          <t>380ms</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 47ms, Avg: 279ms, Max: 1395ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 58ms, Avg: 267ms, Max: 1453ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>255ms</t>
+          <t>564ms</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 60ms, Avg: 276ms, Max: 1239ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 46ms, Avg: 249ms, Max: 1437ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>743ms</t>
+          <t>547ms</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 35ms, Avg: 219ms, Max: 1141ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 43ms, Avg: 248ms, Max: 1120ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>209ms</t>
+          <t>733ms</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 53ms, Avg: 238ms, Max: 1417ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 38ms, Avg: 234ms, Max: 1354ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>520ms</t>
+          <t>678ms</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 48ms, Avg: 261ms, Max: 1423ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 56ms, Avg: 228ms, Max: 1228ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>157ms</t>
+          <t>687ms</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 42ms, Avg: 220ms, Max: 1148ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 50ms, Avg: 255ms, Max: 1402ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>596ms</t>
+          <t>636ms</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 42ms, Avg: 244ms, Max: 1168ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 41ms, Avg: 259ms, Max: 1105ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>842ms</t>
+          <t>714ms</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 47ms, Avg: 221ms, Max: 1106ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 55ms, Avg: 218ms, Max: 1116ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>350ms</t>
+          <t>570ms</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 52ms, Avg: 231ms, Max: 1302ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 55ms, Avg: 227ms, Max: 1297ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>313ms</t>
+          <t>733ms</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 55ms, Avg: 228ms, Max: 1401ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 60ms, Avg: 273ms, Max: 1344ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>633ms</t>
+          <t>376ms</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 57ms, Avg: 223ms, Max: 1200ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 48ms, Avg: 227ms, Max: 1238ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>172ms</t>
+          <t>818ms</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 58ms, Avg: 253ms, Max: 1281ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 40ms, Avg: 223ms, Max: 1161ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>225ms</t>
+          <t>552ms</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 38ms, Avg: 259ms, Max: 1144ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 45ms, Avg: 257ms, Max: 1144ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>224ms</t>
+          <t>750ms</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 41ms, Avg: 232ms, Max: 1459ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 35ms, Avg: 233ms, Max: 1280ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>599ms</t>
+          <t>365ms</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 47ms, Avg: 249ms, Max: 1298ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 53ms, Avg: 255ms, Max: 1376ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>252ms</t>
+          <t>608ms</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 40ms, Avg: 215ms, Max: 1387ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 50ms, Avg: 216ms, Max: 1447ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>234ms</t>
+          <t>758ms</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 42ms, Avg: 245ms, Max: 1384ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 39ms, Avg: 275ms, Max: 1468ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>651ms</t>
+          <t>557ms</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 48ms, Avg: 222ms, Max: 1362ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 55ms, Avg: 226ms, Max: 1473ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>372ms</t>
+          <t>680ms</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 43ms, Avg: 263ms, Max: 1340ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 60ms, Avg: 235ms, Max: 1418ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>668ms</t>
+          <t>282ms</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 48ms, Avg: 228ms, Max: 1250ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 37ms, Avg: 259ms, Max: 1353ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>846ms</t>
+          <t>619ms</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 58ms, Avg: 259ms, Max: 1302ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 60ms, Avg: 258ms, Max: 1251ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>805ms</t>
+          <t>413ms</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 49ms, Avg: 280ms, Max: 1191ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 35ms, Avg: 251ms, Max: 1453ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>644ms</t>
+          <t>808ms</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 59ms, Avg: 212ms, Max: 1393ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 50ms, Avg: 213ms, Max: 1476ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>234ms</t>
+          <t>311ms</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 52ms, Avg: 244ms, Max: 1314ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 39ms, Avg: 255ms, Max: 1450ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>635ms</t>
+          <t>801ms</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 46ms, Avg: 235ms, Max: 1272ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 54ms, Avg: 273ms, Max: 1172ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>178ms</t>
+          <t>457ms</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 45ms, Avg: 214ms, Max: 1329ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 40ms, Avg: 244ms, Max: 1379ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>566ms</t>
+          <t>141ms</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 41ms, Avg: 232ms, Max: 1344ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 55ms, Avg: 267ms, Max: 1342ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>190ms</t>
+          <t>324ms</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 57ms, Avg: 247ms, Max: 1200ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 48ms, Avg: 243ms, Max: 1137ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>460ms</t>
+          <t>539ms</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 49ms, Avg: 236ms, Max: 1107ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 39ms, Avg: 212ms, Max: 1132ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>805ms</t>
+          <t>308ms</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 38ms, Avg: 270ms, Max: 1217ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 59ms, Avg: 223ms, Max: 1401ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>180ms</t>
+          <t>255ms</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 53ms, Avg: 242ms, Max: 1382ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 51ms, Avg: 256ms, Max: 1369ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>785ms</t>
+          <t>651ms</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 59ms, Avg: 262ms, Max: 1153ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 60ms, Avg: 241ms, Max: 1412ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>182ms</t>
+          <t>833ms</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 57ms, Avg: 244ms, Max: 1239ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 49ms, Avg: 243ms, Max: 1479ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>177ms</t>
+          <t>443ms</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 56ms, Avg: 273ms, Max: 1376ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 55ms, Avg: 224ms, Max: 1268ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>282ms</t>
+          <t>521ms</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 44ms, Avg: 217ms, Max: 1218ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 48ms, Avg: 270ms, Max: 1435ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>227ms</t>
+          <t>233ms</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 42ms, Avg: 278ms, Max: 1150ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 54ms, Avg: 274ms, Max: 1235ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>822ms</t>
+          <t>811ms</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 45ms, Avg: 251ms, Max: 1333ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 46ms, Avg: 240ms, Max: 1253ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>358ms</t>
+          <t>515ms</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 38ms, Avg: 277ms, Max: 1415ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 59ms, Avg: 270ms, Max: 1347ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>195ms</t>
+          <t>389ms</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 39ms, Avg: 219ms, Max: 1103ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 53ms, Avg: 221ms, Max: 1234ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>176ms</t>
+          <t>357ms</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 47ms, Avg: 225ms, Max: 1157ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 46ms, Avg: 222ms, Max: 1177ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>156ms</t>
+          <t>531ms</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 55ms, Avg: 229ms, Max: 1360ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 47ms, Avg: 210ms, Max: 1428ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>835ms</t>
+          <t>423ms</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 39ms, Avg: 278ms, Max: 1275ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 43ms, Avg: 211ms, Max: 1388ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>566ms</t>
+          <t>269ms</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 46ms, Avg: 228ms, Max: 1189ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 50ms, Avg: 272ms, Max: 1384ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>846ms</t>
+          <t>604ms</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 57ms, Avg: 229ms, Max: 1470ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 39ms, Avg: 258ms, Max: 1461ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>488ms</t>
+          <t>724ms</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 49ms, Avg: 232ms, Max: 1151ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 59ms, Avg: 278ms, Max: 1291ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>834ms</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 47ms, Avg: 244ms, Max: 1434ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 60ms, Avg: 273ms, Max: 1372ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>317ms</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 38ms, Avg: 262ms, Max: 1344ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 38ms, Avg: 234ms, Max: 1221ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>560ms</t>
+          <t>530ms</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 55ms, Avg: 263ms, Max: 1214ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 52ms, Avg: 249ms, Max: 1446ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>633ms</t>
+          <t>441ms</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 50ms, Avg: 249ms, Max: 1186ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 43ms, Avg: 267ms, Max: 1122ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>755ms</t>
+          <t>326ms</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 52ms, Avg: 236ms, Max: 1226ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 47ms, Avg: 215ms, Max: 1155ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>549ms</t>
+          <t>517ms</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 37ms, Avg: 211ms, Max: 1144ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 42ms, Avg: 215ms, Max: 1160ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>263ms</t>
+          <t>822ms</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 36ms, Avg: 232ms, Max: 1305ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 44ms, Avg: 222ms, Max: 1447ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>412ms</t>
+          <t>818ms</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 58ms, Avg: 263ms, Max: 1306ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 58ms, Avg: 211ms, Max: 1406ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>832ms</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 39ms, Avg: 231ms, Max: 1461ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 39ms, Avg: 247ms, Max: 1328ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>134ms</t>
+          <t>719ms</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 53ms, Avg: 240ms, Max: 1118ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 60ms, Avg: 239ms, Max: 1411ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>809ms</t>
+          <t>562ms</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 55ms, Avg: 220ms, Max: 1163ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 35ms, Avg: 237ms, Max: 1321ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>783ms</t>
+          <t>660ms</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 44ms, Avg: 220ms, Max: 1301ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 36ms, Avg: 261ms, Max: 1203ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>192ms</t>
+          <t>416ms</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 44ms, Avg: 272ms, Max: 1326ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 42ms, Avg: 214ms, Max: 1128ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>831ms</t>
+          <t>250ms</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 36ms, Avg: 241ms, Max: 1105ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 41ms, Avg: 233ms, Max: 1155ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>635ms</t>
+          <t>656ms</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 52ms, Avg: 225ms, Max: 1225ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 55ms, Avg: 227ms, Max: 1354ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -16946,7 +16946,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>506ms</t>
+          <t>306ms</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 60ms, Avg: 216ms, Max: 1439ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 44ms, Avg: 248ms, Max: 1443ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>436ms</t>
+          <t>547ms</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 47ms, Avg: 256ms, Max: 1330ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 60ms, Avg: 210ms, Max: 1472ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>172ms</t>
+          <t>569ms</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 41ms, Avg: 274ms, Max: 1447ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 38ms, Avg: 236ms, Max: 1309ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>617ms</t>
+          <t>700ms</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 48ms, Avg: 242ms, Max: 1450ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 35ms, Avg: 271ms, Max: 1430ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>206ms</t>
+          <t>234ms</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 46ms, Avg: 280ms, Max: 1181ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 51ms, Avg: 230ms, Max: 1279ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>207ms</t>
+          <t>447ms</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 52ms, Avg: 267ms, Max: 1295ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 38ms, Avg: 233ms, Max: 1123ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>641ms</t>
+          <t>431ms</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 52ms, Avg: 242ms, Max: 1377ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 58ms, Avg: 251ms, Max: 1111ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>655ms</t>
+          <t>243ms</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 53ms, Avg: 273ms, Max: 1422ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 52ms, Avg: 260ms, Max: 1241ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>805ms</t>
+          <t>261ms</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 55ms, Avg: 243ms, Max: 1116ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 47ms, Avg: 267ms, Max: 1217ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>723ms</t>
+          <t>246ms</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -17571,7 +17571,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 35ms, Avg: 210ms, Max: 1480ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 51ms, Avg: 278ms, Max: 1411ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>635ms</t>
+          <t>377ms</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 57ms, Avg: 248ms, Max: 1148ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 37ms, Avg: 265ms, Max: 1214ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>453ms</t>
+          <t>470ms</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 46ms, Avg: 238ms, Max: 1467ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 52ms, Avg: 252ms, Max: 1228ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>341ms</t>
+          <t>391ms</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -17763,7 +17763,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 56ms, Avg: 254ms, Max: 1201ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 54ms, Avg: 238ms, Max: 1281ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>281ms</t>
+          <t>662ms</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 58ms, Avg: 211ms, Max: 1296ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 57ms, Avg: 246ms, Max: 1186ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>626ms</t>
+          <t>525ms</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 60ms, Avg: 225ms, Max: 1223ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 54ms, Avg: 261ms, Max: 1314ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -17906,7 +17906,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>574ms</t>
+          <t>278ms</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 52ms, Avg: 277ms, Max: 1319ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 49ms, Avg: 277ms, Max: 1355ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>748ms</t>
+          <t>835ms</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 59ms, Avg: 215ms, Max: 1255ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 51ms, Avg: 262ms, Max: 1357ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>647ms</t>
+          <t>232ms</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -18083,7 +18083,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 48ms, Avg: 267ms, Max: 1269ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 47ms, Avg: 237ms, Max: 1480ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>179ms</t>
+          <t>401ms</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 47ms, Avg: 234ms, Max: 1196ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 43ms, Avg: 229ms, Max: 1250ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>133ms</t>
+          <t>672ms</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 52ms, Avg: 219ms, Max: 1279ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 59ms, Avg: 225ms, Max: 1404ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>775ms</t>
+          <t>377ms</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 50ms, Avg: 239ms, Max: 1263ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 58ms, Avg: 219ms, Max: 1217ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>222ms</t>
+          <t>180ms</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 58ms, Avg: 261ms, Max: 1289ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 60ms, Avg: 238ms, Max: 1218ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>418ms</t>
+          <t>569ms</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Pass. RPS: 123/sec. Latency -&gt; Min: 43ms, Avg: 226ms, Max: 1422ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 43ms, Avg: 277ms, Max: 1208ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>447ms</t>
+          <t>288ms</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Pass. RPS: 114/sec. Latency -&gt; Min: 55ms, Avg: 227ms, Max: 1149ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 39ms, Avg: 270ms, Max: 1102ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -18482,7 +18482,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>371ms</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 56ms, Avg: 230ms, Max: 1315ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 43ms, Avg: 261ms, Max: 1450ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>682ms</t>
+          <t>409ms</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Pass. RPS: 126/sec. Latency -&gt; Min: 50ms, Avg: 213ms, Max: 1242ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 40ms, Avg: 220ms, Max: 1397ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>641ms</t>
+          <t>198ms</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -18659,7 +18659,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 52ms, Avg: 274ms, Max: 1166ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 117/sec. Latency -&gt; Min: 52ms, Avg: 277ms, Max: 1375ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>239ms</t>
+          <t>620ms</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 57ms, Avg: 217ms, Max: 1245ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 50ms, Avg: 272ms, Max: 1378ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>714ms</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 56ms, Avg: 251ms, Max: 1277ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 50ms, Avg: 259ms, Max: 1321ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>446ms</t>
+          <t>154ms</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 37ms, Avg: 216ms, Max: 1168ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 35ms, Avg: 268ms, Max: 1357ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>462ms</t>
+          <t>214ms</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 55ms, Avg: 238ms, Max: 1103ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 36ms, Avg: 238ms, Max: 1211ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>687ms</t>
+          <t>393ms</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Pass. RPS: 116/sec. Latency -&gt; Min: 44ms, Avg: 236ms, Max: 1155ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 46ms, Avg: 241ms, Max: 1240ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>415ms</t>
+          <t>794ms</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 38ms, Avg: 246ms, Max: 1109ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 125/sec. Latency -&gt; Min: 39ms, Avg: 252ms, Max: 1344ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>412ms</t>
+          <t>705ms</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -19107,7 +19107,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 43ms, Avg: 216ms, Max: 1466ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 45ms, Avg: 258ms, Max: 1313ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>355ms</t>
+          <t>177ms</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pass. RPS: 118/sec. Latency -&gt; Min: 53ms, Avg: 239ms, Max: 1337ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 49ms, Avg: 270ms, Max: 1170ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>774ms</t>
+          <t>252ms</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -19235,7 +19235,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 58ms, Avg: 240ms, Max: 1396ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 49ms, Avg: 250ms, Max: 1323ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>829ms</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -19299,7 +19299,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 51ms, Avg: 216ms, Max: 1158ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 124/sec. Latency -&gt; Min: 47ms, Avg: 232ms, Max: 1354ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>320ms</t>
+          <t>537ms</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -19363,7 +19363,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 47ms, Avg: 232ms, Max: 1389ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 119/sec. Latency -&gt; Min: 42ms, Avg: 213ms, Max: 1453ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>483ms</t>
+          <t>806ms</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Pass. RPS: 127/sec. Latency -&gt; Min: 36ms, Avg: 237ms, Max: 1293ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 121/sec. Latency -&gt; Min: 37ms, Avg: 270ms, Max: 1247ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>233ms</t>
+          <t>368ms</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Pass. RPS: 120/sec. Latency -&gt; Min: 56ms, Avg: 212ms, Max: 1206ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 128/sec. Latency -&gt; Min: 36ms, Avg: 225ms, Max: 1198ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>219ms</t>
+          <t>653ms</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 45ms, Avg: 235ms, Max: 1387ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 60ms, Avg: 216ms, Max: 1221ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -19570,7 +19570,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>719ms</t>
+          <t>593ms</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -19619,7 +19619,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Pass. RPS: 122/sec. Latency -&gt; Min: 55ms, Avg: 278ms, Max: 1375ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 113/sec. Latency -&gt; Min: 58ms, Avg: 246ms, Max: 1220ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>464ms</t>
+          <t>681ms</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Pass. RPS: 115/sec. Latency -&gt; Min: 37ms, Avg: 266ms, Max: 1239ms. Error Rate: 0.00%.</t>
+          <t>Pass. RPS: 112/sec. Latency -&gt; Min: 50ms, Avg: 227ms, Max: 1234ms. Error Rate: 0.00%.</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>824ms</t>
+          <t>502ms</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
